--- a/priorizacion_municipios_jalisco V28042026 (1).xlsx
+++ b/priorizacion_municipios_jalisco V28042026 (1).xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BJ126"/>
+  <dimension ref="A1:BL126"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -706,35 +706,45 @@
       </c>
       <c r="BD1" s="1" t="inlineStr">
         <is>
+          <t>dm2_total_con_pandemia</t>
+        </is>
+      </c>
+      <c r="BE1" s="1" t="inlineStr">
+        <is>
+          <t>dm2_total_excl_pandemia</t>
+        </is>
+      </c>
+      <c r="BF1" s="1" t="inlineStr">
+        <is>
+          <t>dm2_basica_pandemia</t>
+        </is>
+      </c>
+      <c r="BG1" s="1" t="inlineStr">
+        <is>
+          <t>dm2_contrib_pandemia</t>
+        </is>
+      </c>
+      <c r="BH1" s="1" t="inlineStr">
+        <is>
           <t>tasa_aj_basica_2018</t>
         </is>
       </c>
-      <c r="BE1" s="1" t="inlineStr">
+      <c r="BI1" s="1" t="inlineStr">
         <is>
           <t>tasa_aj_general_2018</t>
         </is>
       </c>
-      <c r="BF1" s="1" t="inlineStr">
+      <c r="BJ1" s="1" t="inlineStr">
         <is>
           <t>tasa_aj_basica_2025</t>
         </is>
       </c>
-      <c r="BG1" s="1" t="inlineStr">
+      <c r="BK1" s="1" t="inlineStr">
         <is>
           <t>tasa_aj_general_2025</t>
         </is>
       </c>
-      <c r="BH1" s="1" t="inlineStr">
-        <is>
-          <t>dm2_total_con_pandemia</t>
-        </is>
-      </c>
-      <c r="BI1" s="1" t="inlineStr">
-        <is>
-          <t>dm2_total_excl_pandemia</t>
-        </is>
-      </c>
-      <c r="BJ1" s="1" t="inlineStr">
+      <c r="BL1" s="1" t="inlineStr">
         <is>
           <t>tasa_cruda_comparable</t>
         </is>
@@ -907,24 +917,30 @@
         <v>-103.3555207</v>
       </c>
       <c r="BD2" t="n">
+        <v>290</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>203</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>152</v>
+      </c>
+      <c r="BG2" t="n">
+        <v>138</v>
+      </c>
+      <c r="BH2" t="n">
         <v>76.09999999999999</v>
       </c>
-      <c r="BE2" t="n">
+      <c r="BI2" t="n">
         <v>126.8</v>
       </c>
-      <c r="BF2" t="n">
+      <c r="BJ2" t="n">
         <v>38.2</v>
       </c>
-      <c r="BG2" t="n">
+      <c r="BK2" t="n">
         <v>127.5</v>
       </c>
-      <c r="BH2" t="n">
-        <v>290</v>
-      </c>
-      <c r="BI2" t="n">
-        <v>203</v>
-      </c>
-      <c r="BJ2" t="n">
+      <c r="BL2" t="n">
         <v>287.5</v>
       </c>
     </row>
@@ -1095,24 +1111,30 @@
         <v>-102.7767999</v>
       </c>
       <c r="BD3" t="n">
+        <v>90</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>66</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>33</v>
+      </c>
+      <c r="BG3" t="n">
+        <v>57</v>
+      </c>
+      <c r="BH3" t="n">
         <v>19.7</v>
       </c>
-      <c r="BE3" t="n">
+      <c r="BI3" t="n">
         <v>61.8</v>
       </c>
-      <c r="BF3" t="n">
+      <c r="BJ3" t="n">
         <v>50.4</v>
       </c>
-      <c r="BG3" t="n">
+      <c r="BK3" t="n">
         <v>94.7</v>
       </c>
-      <c r="BH3" t="n">
-        <v>90</v>
-      </c>
-      <c r="BI3" t="n">
-        <v>66</v>
-      </c>
-      <c r="BJ3" t="n">
+      <c r="BL3" t="n">
         <v>198.8</v>
       </c>
     </row>
@@ -1283,24 +1305,30 @@
         <v>-102.8896944</v>
       </c>
       <c r="BD4" t="n">
+        <v>79</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>50</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>37</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>42</v>
+      </c>
+      <c r="BH4" t="n">
         <v>39.1</v>
       </c>
-      <c r="BE4" t="n">
+      <c r="BI4" t="n">
         <v>95.90000000000001</v>
       </c>
-      <c r="BF4" t="n">
+      <c r="BJ4" t="n">
         <v>57.5</v>
       </c>
-      <c r="BG4" t="n">
+      <c r="BK4" t="n">
         <v>64.59999999999999</v>
       </c>
-      <c r="BH4" t="n">
-        <v>79</v>
-      </c>
-      <c r="BI4" t="n">
-        <v>50</v>
-      </c>
-      <c r="BJ4" t="n">
+      <c r="BL4" t="n">
         <v>86.8</v>
       </c>
     </row>
@@ -1469,24 +1497,30 @@
         <v>-103.8934971</v>
       </c>
       <c r="BD5" t="n">
+        <v>51</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>33</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>20</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>31</v>
+      </c>
+      <c r="BH5" t="n">
         <v>17.1</v>
       </c>
-      <c r="BE5" t="n">
+      <c r="BI5" t="n">
         <v>61.3</v>
       </c>
-      <c r="BF5" t="n">
+      <c r="BJ5" t="n">
         <v>97</v>
       </c>
-      <c r="BG5" t="n">
+      <c r="BK5" t="n">
         <v>158.4</v>
       </c>
-      <c r="BH5" t="n">
-        <v>51</v>
-      </c>
-      <c r="BI5" t="n">
-        <v>33</v>
-      </c>
-      <c r="BJ5" t="n">
+      <c r="BL5" t="n">
         <v>76.90000000000001</v>
       </c>
     </row>
@@ -1657,24 +1691,30 @@
         <v>-104.4739578</v>
       </c>
       <c r="BD6" t="n">
+        <v>202</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>138</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>141</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>61</v>
+      </c>
+      <c r="BH6" t="n">
         <v>60.5</v>
       </c>
-      <c r="BE6" t="n">
+      <c r="BI6" t="n">
         <v>109.4</v>
       </c>
-      <c r="BF6" t="n">
+      <c r="BJ6" t="n">
         <v>70.59999999999999</v>
       </c>
-      <c r="BG6" t="n">
+      <c r="BK6" t="n">
         <v>118.3</v>
       </c>
-      <c r="BH6" t="n">
-        <v>202</v>
-      </c>
-      <c r="BI6" t="n">
-        <v>138</v>
-      </c>
-      <c r="BJ6" t="n">
+      <c r="BL6" t="n">
         <v>172.5</v>
       </c>
     </row>
@@ -1843,24 +1883,30 @@
         <v>-103.2320743</v>
       </c>
       <c r="BD7" t="n">
+        <v>113</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>81</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>55</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>58</v>
+      </c>
+      <c r="BH7" t="n">
         <v>94.59999999999999</v>
       </c>
-      <c r="BE7" t="n">
+      <c r="BI7" t="n">
         <v>171.1</v>
       </c>
-      <c r="BF7" t="n">
+      <c r="BJ7" t="n">
         <v>35.9</v>
       </c>
-      <c r="BG7" t="n">
+      <c r="BK7" t="n">
         <v>85.3</v>
       </c>
-      <c r="BH7" t="n">
-        <v>113</v>
-      </c>
-      <c r="BI7" t="n">
-        <v>81</v>
-      </c>
-      <c r="BJ7" t="n">
+      <c r="BL7" t="n">
         <v>204.9</v>
       </c>
     </row>
@@ -2029,24 +2075,30 @@
         <v>-102.1075738</v>
       </c>
       <c r="BD8" t="n">
+        <v>323</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>229</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>191</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>132</v>
+      </c>
+      <c r="BH8" t="n">
         <v>106.2</v>
       </c>
-      <c r="BE8" t="n">
+      <c r="BI8" t="n">
         <v>153.6</v>
       </c>
-      <c r="BF8" t="n">
+      <c r="BJ8" t="n">
         <v>75.8</v>
       </c>
-      <c r="BG8" t="n">
+      <c r="BK8" t="n">
         <v>127.5</v>
       </c>
-      <c r="BH8" t="n">
-        <v>323</v>
-      </c>
-      <c r="BI8" t="n">
-        <v>229</v>
-      </c>
-      <c r="BJ8" t="n">
+      <c r="BL8" t="n">
         <v>199.3</v>
       </c>
     </row>
@@ -2217,24 +2269,30 @@
         <v>-103.6790517</v>
       </c>
       <c r="BD9" t="n">
+        <v>91</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>49</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>38</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>53</v>
+      </c>
+      <c r="BH9" t="n">
         <v>20.5</v>
       </c>
-      <c r="BE9" t="n">
+      <c r="BI9" t="n">
         <v>60.9</v>
       </c>
-      <c r="BF9" t="n">
+      <c r="BJ9" t="n">
         <v>76.40000000000001</v>
       </c>
-      <c r="BG9" t="n">
+      <c r="BK9" t="n">
         <v>113.2</v>
       </c>
-      <c r="BH9" t="n">
-        <v>91</v>
-      </c>
-      <c r="BI9" t="n">
-        <v>49</v>
-      </c>
-      <c r="BJ9" t="n">
+      <c r="BL9" t="n">
         <v>155.9</v>
       </c>
     </row>
@@ -2403,24 +2461,30 @@
         <v>-103.9182009</v>
       </c>
       <c r="BD10" t="n">
+        <v>114</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>86</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>42</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>72</v>
+      </c>
+      <c r="BH10" t="n">
         <v>86.90000000000001</v>
       </c>
-      <c r="BE10" t="n">
+      <c r="BI10" t="n">
         <v>105.3</v>
       </c>
-      <c r="BF10" t="n">
+      <c r="BJ10" t="n">
         <v>11</v>
       </c>
-      <c r="BG10" t="n">
+      <c r="BK10" t="n">
         <v>122.5</v>
       </c>
-      <c r="BH10" t="n">
-        <v>114</v>
-      </c>
-      <c r="BI10" t="n">
-        <v>86</v>
-      </c>
-      <c r="BJ10" t="n">
+      <c r="BL10" t="n">
         <v>239.1</v>
       </c>
     </row>
@@ -2589,24 +2653,30 @@
         <v>-103.4433689</v>
       </c>
       <c r="BD11" t="n">
+        <v>79</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>52</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>40</v>
+      </c>
+      <c r="BG11" t="n">
+        <v>39</v>
+      </c>
+      <c r="BH11" t="n">
         <v>101.7</v>
       </c>
-      <c r="BE11" t="n">
+      <c r="BI11" t="n">
         <v>149.3</v>
       </c>
-      <c r="BF11" t="n">
+      <c r="BJ11" t="n">
         <v>47.3</v>
       </c>
-      <c r="BG11" t="n">
+      <c r="BK11" t="n">
         <v>112.7</v>
       </c>
-      <c r="BH11" t="n">
-        <v>79</v>
-      </c>
-      <c r="BI11" t="n">
-        <v>52</v>
-      </c>
-      <c r="BJ11" t="n">
+      <c r="BL11" t="n">
         <v>210.3</v>
       </c>
     </row>
@@ -2777,24 +2847,30 @@
         <v>-103.307062</v>
       </c>
       <c r="BD12" t="n">
+        <v>271</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>187</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>144</v>
+      </c>
+      <c r="BG12" t="n">
+        <v>126</v>
+      </c>
+      <c r="BH12" t="n">
         <v>86.59999999999999</v>
       </c>
-      <c r="BE12" t="n">
+      <c r="BI12" t="n">
         <v>155.9</v>
       </c>
-      <c r="BF12" t="n">
+      <c r="BJ12" t="n">
         <v>77.8</v>
       </c>
-      <c r="BG12" t="n">
+      <c r="BK12" t="n">
         <v>103.7</v>
       </c>
-      <c r="BH12" t="n">
-        <v>271</v>
-      </c>
-      <c r="BI12" t="n">
-        <v>187</v>
-      </c>
-      <c r="BJ12" t="n">
+      <c r="BL12" t="n">
         <v>195.6</v>
       </c>
     </row>
@@ -2963,24 +3039,30 @@
         <v>-103.5300375</v>
       </c>
       <c r="BD13" t="n">
+        <v>174</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>108</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>93</v>
+      </c>
+      <c r="BG13" t="n">
+        <v>81</v>
+      </c>
+      <c r="BH13" t="n">
         <v>81.2</v>
       </c>
-      <c r="BE13" t="n">
+      <c r="BI13" t="n">
         <v>118.6</v>
       </c>
-      <c r="BF13" t="n">
+      <c r="BJ13" t="n">
         <v>37</v>
       </c>
-      <c r="BG13" t="n">
+      <c r="BK13" t="n">
         <v>87.40000000000001</v>
       </c>
-      <c r="BH13" t="n">
-        <v>174</v>
-      </c>
-      <c r="BI13" t="n">
-        <v>108</v>
-      </c>
-      <c r="BJ13" t="n">
+      <c r="BL13" t="n">
         <v>233.5</v>
       </c>
     </row>
@@ -3151,24 +3233,30 @@
         <v>-103.5802255</v>
       </c>
       <c r="BD14" t="n">
+        <v>67</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>49</v>
+      </c>
+      <c r="BF14" t="n">
+        <v>28</v>
+      </c>
+      <c r="BG14" t="n">
+        <v>39</v>
+      </c>
+      <c r="BH14" t="n">
         <v>89.8</v>
       </c>
-      <c r="BE14" t="n">
+      <c r="BI14" t="n">
         <v>160.6</v>
       </c>
-      <c r="BF14" t="n">
+      <c r="BJ14" t="n">
         <v>75.59999999999999</v>
       </c>
-      <c r="BG14" t="n">
+      <c r="BK14" t="n">
         <v>110.3</v>
       </c>
-      <c r="BH14" t="n">
-        <v>67</v>
-      </c>
-      <c r="BI14" t="n">
-        <v>49</v>
-      </c>
-      <c r="BJ14" t="n">
+      <c r="BL14" t="n">
         <v>187.5</v>
       </c>
     </row>
@@ -3339,24 +3427,30 @@
         <v>-103.4472817</v>
       </c>
       <c r="BD15" t="n">
+        <v>171</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>117</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>83</v>
+      </c>
+      <c r="BG15" t="n">
+        <v>88</v>
+      </c>
+      <c r="BH15" t="n">
         <v>58.1</v>
       </c>
-      <c r="BE15" t="n">
+      <c r="BI15" t="n">
         <v>129.8</v>
       </c>
-      <c r="BF15" t="n">
+      <c r="BJ15" t="n">
         <v>48.1</v>
       </c>
-      <c r="BG15" t="n">
+      <c r="BK15" t="n">
         <v>116.3</v>
       </c>
-      <c r="BH15" t="n">
-        <v>171</v>
-      </c>
-      <c r="BI15" t="n">
-        <v>117</v>
-      </c>
-      <c r="BJ15" t="n">
+      <c r="BL15" t="n">
         <v>213.8</v>
       </c>
     </row>
@@ -3527,24 +3621,30 @@
         <v>-104.2810261</v>
       </c>
       <c r="BD16" t="n">
+        <v>94</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>47</v>
+      </c>
+      <c r="BF16" t="n">
+        <v>35</v>
+      </c>
+      <c r="BG16" t="n">
+        <v>59</v>
+      </c>
+      <c r="BH16" t="n">
         <v>33.7</v>
       </c>
-      <c r="BE16" t="n">
+      <c r="BI16" t="n">
         <v>125.2</v>
       </c>
-      <c r="BF16" t="n">
+      <c r="BJ16" t="n">
         <v>15.3</v>
       </c>
-      <c r="BG16" t="n">
+      <c r="BK16" t="n">
         <v>43.5</v>
       </c>
-      <c r="BH16" t="n">
-        <v>94</v>
-      </c>
-      <c r="BI16" t="n">
-        <v>47</v>
-      </c>
-      <c r="BJ16" t="n">
+      <c r="BL16" t="n">
         <v>136.4</v>
       </c>
     </row>
@@ -3715,24 +3815,30 @@
         <v>-104.4748712</v>
       </c>
       <c r="BD17" t="n">
+        <v>453</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>312</v>
+      </c>
+      <c r="BF17" t="n">
+        <v>214</v>
+      </c>
+      <c r="BG17" t="n">
+        <v>239</v>
+      </c>
+      <c r="BH17" t="n">
         <v>101.3</v>
       </c>
-      <c r="BE17" t="n">
+      <c r="BI17" t="n">
         <v>211.3</v>
       </c>
-      <c r="BF17" t="n">
+      <c r="BJ17" t="n">
         <v>109.7</v>
       </c>
-      <c r="BG17" t="n">
+      <c r="BK17" t="n">
         <v>165.7</v>
       </c>
-      <c r="BH17" t="n">
-        <v>453</v>
-      </c>
-      <c r="BI17" t="n">
-        <v>312</v>
-      </c>
-      <c r="BJ17" t="n">
+      <c r="BL17" t="n">
         <v>250.1</v>
       </c>
     </row>
@@ -3903,24 +4009,30 @@
         <v>-103.2825505</v>
       </c>
       <c r="BD18" t="n">
+        <v>86</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>54</v>
+      </c>
+      <c r="BF18" t="n">
+        <v>40</v>
+      </c>
+      <c r="BG18" t="n">
+        <v>46</v>
+      </c>
+      <c r="BH18" t="n">
         <v>60.6</v>
       </c>
-      <c r="BE18" t="n">
+      <c r="BI18" t="n">
         <v>85.90000000000001</v>
       </c>
-      <c r="BF18" t="n">
+      <c r="BJ18" t="n">
         <v>25.2</v>
       </c>
-      <c r="BG18" t="n">
+      <c r="BK18" t="n">
         <v>49.2</v>
       </c>
-      <c r="BH18" t="n">
-        <v>86</v>
-      </c>
-      <c r="BI18" t="n">
-        <v>54</v>
-      </c>
-      <c r="BJ18" t="n">
+      <c r="BL18" t="n">
         <v>144.9</v>
       </c>
     </row>
@@ -4089,24 +4201,30 @@
         <v>-103.0970335</v>
       </c>
       <c r="BD19" t="n">
+        <v>65</v>
+      </c>
+      <c r="BE19" t="n">
+        <v>44</v>
+      </c>
+      <c r="BF19" t="n">
+        <v>26</v>
+      </c>
+      <c r="BG19" t="n">
+        <v>39</v>
+      </c>
+      <c r="BH19" t="n">
         <v>12.8</v>
       </c>
-      <c r="BE19" t="n">
+      <c r="BI19" t="n">
         <v>57</v>
       </c>
-      <c r="BF19" t="n">
+      <c r="BJ19" t="n">
         <v>39.5</v>
       </c>
-      <c r="BG19" t="n">
+      <c r="BK19" t="n">
         <v>80.40000000000001</v>
       </c>
-      <c r="BH19" t="n">
-        <v>65</v>
-      </c>
-      <c r="BI19" t="n">
-        <v>44</v>
-      </c>
-      <c r="BJ19" t="n">
+      <c r="BL19" t="n">
         <v>162.4</v>
       </c>
     </row>
@@ -4275,24 +4393,30 @@
         <v>-104.1187354</v>
       </c>
       <c r="BD20" t="n">
+        <v>110</v>
+      </c>
+      <c r="BE20" t="n">
+        <v>80</v>
+      </c>
+      <c r="BF20" t="n">
+        <v>73</v>
+      </c>
+      <c r="BG20" t="n">
+        <v>37</v>
+      </c>
+      <c r="BH20" t="n">
         <v>72.09999999999999</v>
       </c>
-      <c r="BE20" t="n">
+      <c r="BI20" t="n">
         <v>127.1</v>
       </c>
-      <c r="BF20" t="n">
+      <c r="BJ20" t="n">
         <v>37.6</v>
       </c>
-      <c r="BG20" t="n">
+      <c r="BK20" t="n">
         <v>115.3</v>
       </c>
-      <c r="BH20" t="n">
-        <v>110</v>
-      </c>
-      <c r="BI20" t="n">
-        <v>80</v>
-      </c>
-      <c r="BJ20" t="n">
+      <c r="BL20" t="n">
         <v>247.4</v>
       </c>
     </row>
@@ -4463,24 +4587,30 @@
         <v>-103.7478804</v>
       </c>
       <c r="BD21" t="n">
+        <v>289</v>
+      </c>
+      <c r="BE21" t="n">
+        <v>188</v>
+      </c>
+      <c r="BF21" t="n">
+        <v>140</v>
+      </c>
+      <c r="BG21" t="n">
+        <v>149</v>
+      </c>
+      <c r="BH21" t="n">
         <v>56</v>
       </c>
-      <c r="BE21" t="n">
+      <c r="BI21" t="n">
         <v>138.2</v>
       </c>
-      <c r="BF21" t="n">
+      <c r="BJ21" t="n">
         <v>56.5</v>
       </c>
-      <c r="BG21" t="n">
+      <c r="BK21" t="n">
         <v>87.2</v>
       </c>
-      <c r="BH21" t="n">
-        <v>289</v>
-      </c>
-      <c r="BI21" t="n">
-        <v>188</v>
-      </c>
-      <c r="BJ21" t="n">
+      <c r="BL21" t="n">
         <v>180.2</v>
       </c>
     </row>
@@ -4649,24 +4779,30 @@
         <v>-103.9734455</v>
       </c>
       <c r="BD22" t="n">
+        <v>132</v>
+      </c>
+      <c r="BE22" t="n">
+        <v>86</v>
+      </c>
+      <c r="BF22" t="n">
+        <v>70</v>
+      </c>
+      <c r="BG22" t="n">
+        <v>62</v>
+      </c>
+      <c r="BH22" t="n">
         <v>71.2</v>
       </c>
-      <c r="BE22" t="n">
+      <c r="BI22" t="n">
         <v>125.6</v>
       </c>
-      <c r="BF22" t="n">
+      <c r="BJ22" t="n">
         <v>20.4</v>
       </c>
-      <c r="BG22" t="n">
+      <c r="BK22" t="n">
         <v>38.4</v>
       </c>
-      <c r="BH22" t="n">
-        <v>132</v>
-      </c>
-      <c r="BI22" t="n">
-        <v>86</v>
-      </c>
-      <c r="BJ22" t="n">
+      <c r="BL22" t="n">
         <v>119.2</v>
       </c>
     </row>
@@ -4835,24 +4971,30 @@
         <v>-102.158357</v>
       </c>
       <c r="BD23" t="n">
+        <v>223</v>
+      </c>
+      <c r="BE23" t="n">
+        <v>152</v>
+      </c>
+      <c r="BF23" t="n">
+        <v>134</v>
+      </c>
+      <c r="BG23" t="n">
+        <v>89</v>
+      </c>
+      <c r="BH23" t="n">
         <v>96.7</v>
       </c>
-      <c r="BE23" t="n">
+      <c r="BI23" t="n">
         <v>131.2</v>
       </c>
-      <c r="BF23" t="n">
+      <c r="BJ23" t="n">
         <v>66.8</v>
       </c>
-      <c r="BG23" t="n">
+      <c r="BK23" t="n">
         <v>118.7</v>
       </c>
-      <c r="BH23" t="n">
-        <v>223</v>
-      </c>
-      <c r="BI23" t="n">
-        <v>152</v>
-      </c>
-      <c r="BJ23" t="n">
+      <c r="BL23" t="n">
         <v>142.4</v>
       </c>
     </row>
@@ -5023,24 +5165,30 @@
         <v>-104.4154127</v>
       </c>
       <c r="BD24" t="n">
+        <v>77</v>
+      </c>
+      <c r="BE24" t="n">
+        <v>50</v>
+      </c>
+      <c r="BF24" t="n">
+        <v>38</v>
+      </c>
+      <c r="BG24" t="n">
+        <v>39</v>
+      </c>
+      <c r="BH24" t="n">
         <v>68.40000000000001</v>
       </c>
-      <c r="BE24" t="n">
+      <c r="BI24" t="n">
         <v>96.90000000000001</v>
       </c>
-      <c r="BF24" t="n">
+      <c r="BJ24" t="n">
         <v>26.9</v>
       </c>
-      <c r="BG24" t="n">
+      <c r="BK24" t="n">
         <v>75.7</v>
       </c>
-      <c r="BH24" t="n">
-        <v>77</v>
-      </c>
-      <c r="BI24" t="n">
-        <v>50</v>
-      </c>
-      <c r="BJ24" t="n">
+      <c r="BL24" t="n">
         <v>196.8</v>
       </c>
     </row>
@@ -5211,24 +5359,30 @@
         <v>-103.189394</v>
       </c>
       <c r="BD25" t="n">
+        <v>127</v>
+      </c>
+      <c r="BE25" t="n">
+        <v>76</v>
+      </c>
+      <c r="BF25" t="n">
+        <v>81</v>
+      </c>
+      <c r="BG25" t="n">
+        <v>46</v>
+      </c>
+      <c r="BH25" t="n">
         <v>29.1</v>
       </c>
-      <c r="BE25" t="n">
+      <c r="BI25" t="n">
         <v>70.2</v>
       </c>
-      <c r="BF25" t="n">
+      <c r="BJ25" t="n">
         <v>105.9</v>
       </c>
-      <c r="BG25" t="n">
+      <c r="BK25" t="n">
         <v>121.2</v>
       </c>
-      <c r="BH25" t="n">
-        <v>127</v>
-      </c>
-      <c r="BI25" t="n">
-        <v>76</v>
-      </c>
-      <c r="BJ25" t="n">
+      <c r="BL25" t="n">
         <v>174.6</v>
       </c>
     </row>
@@ -5399,24 +5553,30 @@
         <v>-103.1889901</v>
       </c>
       <c r="BD26" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="BE26" t="n">
+        <v>33</v>
+      </c>
+      <c r="BF26" t="n">
+        <v>21</v>
+      </c>
+      <c r="BG26" t="n">
+        <v>34</v>
+      </c>
+      <c r="BH26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI26" t="n">
         <v>92.59999999999999</v>
       </c>
-      <c r="BF26" t="n">
+      <c r="BJ26" t="n">
         <v>69.90000000000001</v>
       </c>
-      <c r="BG26" t="n">
+      <c r="BK26" t="n">
         <v>75.5</v>
       </c>
-      <c r="BH26" t="n">
-        <v>55</v>
-      </c>
-      <c r="BI26" t="n">
-        <v>33</v>
-      </c>
-      <c r="BJ26" t="n">
+      <c r="BL26" t="n">
         <v>137.2</v>
       </c>
     </row>
@@ -5585,24 +5745,30 @@
         <v>-103.6302229</v>
       </c>
       <c r="BD27" t="n">
+        <v>102</v>
+      </c>
+      <c r="BE27" t="n">
+        <v>63</v>
+      </c>
+      <c r="BF27" t="n">
+        <v>37</v>
+      </c>
+      <c r="BG27" t="n">
+        <v>65</v>
+      </c>
+      <c r="BH27" t="n">
         <v>58.5</v>
       </c>
-      <c r="BE27" t="n">
+      <c r="BI27" t="n">
         <v>84</v>
       </c>
-      <c r="BF27" t="n">
+      <c r="BJ27" t="n">
         <v>11.9</v>
       </c>
-      <c r="BG27" t="n">
+      <c r="BK27" t="n">
         <v>156.3</v>
       </c>
-      <c r="BH27" t="n">
-        <v>102</v>
-      </c>
-      <c r="BI27" t="n">
-        <v>63</v>
-      </c>
-      <c r="BJ27" t="n">
+      <c r="BL27" t="n">
         <v>171.9</v>
       </c>
     </row>
@@ -5773,24 +5939,30 @@
         <v>-104.1426131</v>
       </c>
       <c r="BD28" t="n">
+        <v>144</v>
+      </c>
+      <c r="BE28" t="n">
+        <v>92</v>
+      </c>
+      <c r="BF28" t="n">
+        <v>76</v>
+      </c>
+      <c r="BG28" t="n">
+        <v>68</v>
+      </c>
+      <c r="BH28" t="n">
         <v>29.3</v>
       </c>
-      <c r="BE28" t="n">
+      <c r="BI28" t="n">
         <v>67.2</v>
       </c>
-      <c r="BF28" t="n">
+      <c r="BJ28" t="n">
         <v>41.3</v>
       </c>
-      <c r="BG28" t="n">
+      <c r="BK28" t="n">
         <v>90.7</v>
       </c>
-      <c r="BH28" t="n">
-        <v>144</v>
-      </c>
-      <c r="BI28" t="n">
-        <v>92</v>
-      </c>
-      <c r="BJ28" t="n">
+      <c r="BL28" t="n">
         <v>201.6</v>
       </c>
     </row>
@@ -5961,24 +6133,30 @@
         <v>-104.358185</v>
       </c>
       <c r="BD29" t="n">
+        <v>234</v>
+      </c>
+      <c r="BE29" t="n">
+        <v>148</v>
+      </c>
+      <c r="BF29" t="n">
+        <v>123</v>
+      </c>
+      <c r="BG29" t="n">
+        <v>111</v>
+      </c>
+      <c r="BH29" t="n">
         <v>49.7</v>
       </c>
-      <c r="BE29" t="n">
+      <c r="BI29" t="n">
         <v>82.40000000000001</v>
       </c>
-      <c r="BF29" t="n">
+      <c r="BJ29" t="n">
         <v>55.6</v>
       </c>
-      <c r="BG29" t="n">
+      <c r="BK29" t="n">
         <v>92.8</v>
       </c>
-      <c r="BH29" t="n">
-        <v>234</v>
-      </c>
-      <c r="BI29" t="n">
-        <v>148</v>
-      </c>
-      <c r="BJ29" t="n">
+      <c r="BL29" t="n">
         <v>130.8</v>
       </c>
     </row>
@@ -6149,24 +6327,30 @@
         <v>-103.338396</v>
       </c>
       <c r="BD30" t="n">
+        <v>23987</v>
+      </c>
+      <c r="BE30" t="n">
+        <v>15273</v>
+      </c>
+      <c r="BF30" t="n">
+        <v>10690</v>
+      </c>
+      <c r="BG30" t="n">
+        <v>13285</v>
+      </c>
+      <c r="BH30" t="n">
         <v>68.59999999999999</v>
       </c>
-      <c r="BE30" t="n">
+      <c r="BI30" t="n">
         <v>143.4</v>
       </c>
-      <c r="BF30" t="n">
+      <c r="BJ30" t="n">
         <v>45.6</v>
       </c>
-      <c r="BG30" t="n">
+      <c r="BK30" t="n">
         <v>89</v>
       </c>
-      <c r="BH30" t="n">
-        <v>23988</v>
-      </c>
-      <c r="BI30" t="n">
-        <v>15273</v>
-      </c>
-      <c r="BJ30" t="n">
+      <c r="BL30" t="n">
         <v>183.5</v>
       </c>
     </row>
@@ -6335,24 +6519,30 @@
         <v>-105.4242415</v>
       </c>
       <c r="BD31" t="n">
+        <v>132</v>
+      </c>
+      <c r="BE31" t="n">
+        <v>90</v>
+      </c>
+      <c r="BF31" t="n">
+        <v>65</v>
+      </c>
+      <c r="BG31" t="n">
+        <v>67</v>
+      </c>
+      <c r="BH31" t="n">
         <v>48.6</v>
       </c>
-      <c r="BE31" t="n">
+      <c r="BI31" t="n">
         <v>124</v>
       </c>
-      <c r="BF31" t="n">
+      <c r="BJ31" t="n">
         <v>59.9</v>
       </c>
-      <c r="BG31" t="n">
+      <c r="BK31" t="n">
         <v>94</v>
       </c>
-      <c r="BH31" t="n">
-        <v>132</v>
-      </c>
-      <c r="BI31" t="n">
-        <v>90</v>
-      </c>
-      <c r="BJ31" t="n">
+      <c r="BL31" t="n">
         <v>129.5</v>
       </c>
     </row>
@@ -6523,24 +6713,30 @@
         <v>-104.6049737</v>
       </c>
       <c r="BD32" t="n">
+        <v>632</v>
+      </c>
+      <c r="BE32" t="n">
+        <v>413</v>
+      </c>
+      <c r="BF32" t="n">
+        <v>318</v>
+      </c>
+      <c r="BG32" t="n">
+        <v>314</v>
+      </c>
+      <c r="BH32" t="n">
         <v>94.90000000000001</v>
       </c>
-      <c r="BE32" t="n">
+      <c r="BI32" t="n">
         <v>147.3</v>
       </c>
-      <c r="BF32" t="n">
+      <c r="BJ32" t="n">
         <v>63.7</v>
       </c>
-      <c r="BG32" t="n">
+      <c r="BK32" t="n">
         <v>119.6</v>
       </c>
-      <c r="BH32" t="n">
-        <v>632</v>
-      </c>
-      <c r="BI32" t="n">
-        <v>413</v>
-      </c>
-      <c r="BJ32" t="n">
+      <c r="BL32" t="n">
         <v>169.3</v>
       </c>
     </row>
@@ -6709,24 +6905,30 @@
         <v>-103.7488329</v>
       </c>
       <c r="BD33" t="n">
+        <v>95</v>
+      </c>
+      <c r="BE33" t="n">
+        <v>66</v>
+      </c>
+      <c r="BF33" t="n">
+        <v>56</v>
+      </c>
+      <c r="BG33" t="n">
+        <v>39</v>
+      </c>
+      <c r="BH33" t="n">
         <v>85.5</v>
       </c>
-      <c r="BE33" t="n">
+      <c r="BI33" t="n">
         <v>108.7</v>
       </c>
-      <c r="BF33" t="n">
+      <c r="BJ33" t="n">
         <v>73.40000000000001</v>
       </c>
-      <c r="BG33" t="n">
+      <c r="BK33" t="n">
         <v>89.59999999999999</v>
       </c>
-      <c r="BH33" t="n">
-        <v>95</v>
-      </c>
-      <c r="BI33" t="n">
-        <v>66</v>
-      </c>
-      <c r="BJ33" t="n">
+      <c r="BL33" t="n">
         <v>140.2</v>
       </c>
     </row>
@@ -6897,24 +7099,30 @@
         <v>-104.5302158</v>
       </c>
       <c r="BD34" t="n">
+        <v>70</v>
+      </c>
+      <c r="BE34" t="n">
+        <v>53</v>
+      </c>
+      <c r="BF34" t="n">
+        <v>48</v>
+      </c>
+      <c r="BG34" t="n">
+        <v>22</v>
+      </c>
+      <c r="BH34" t="n">
         <v>31.1</v>
       </c>
-      <c r="BE34" t="n">
+      <c r="BI34" t="n">
         <v>68.5</v>
       </c>
-      <c r="BF34" t="n">
+      <c r="BJ34" t="n">
         <v>69.8</v>
       </c>
-      <c r="BG34" t="n">
+      <c r="BK34" t="n">
         <v>132.6</v>
       </c>
-      <c r="BH34" t="n">
-        <v>70</v>
-      </c>
-      <c r="BI34" t="n">
-        <v>53</v>
-      </c>
-      <c r="BJ34" t="n">
+      <c r="BL34" t="n">
         <v>198.2</v>
       </c>
     </row>
@@ -7085,24 +7293,30 @@
         <v>-104.5335287</v>
       </c>
       <c r="BD35" t="n">
+        <v>61</v>
+      </c>
+      <c r="BE35" t="n">
+        <v>41</v>
+      </c>
+      <c r="BF35" t="n">
+        <v>44</v>
+      </c>
+      <c r="BG35" t="n">
+        <v>17</v>
+      </c>
+      <c r="BH35" t="n">
         <v>42.9</v>
       </c>
-      <c r="BE35" t="n">
+      <c r="BI35" t="n">
         <v>91.40000000000001</v>
       </c>
-      <c r="BF35" t="n">
+      <c r="BJ35" t="n">
         <v>68.40000000000001</v>
       </c>
-      <c r="BG35" t="n">
+      <c r="BK35" t="n">
         <v>76.2</v>
       </c>
-      <c r="BH35" t="n">
-        <v>61</v>
-      </c>
-      <c r="BI35" t="n">
-        <v>41</v>
-      </c>
-      <c r="BJ35" t="n">
+      <c r="BL35" t="n">
         <v>181.6</v>
       </c>
     </row>
@@ -7273,24 +7487,30 @@
         <v>-104.2276769</v>
       </c>
       <c r="BD36" t="n">
+        <v>254</v>
+      </c>
+      <c r="BE36" t="n">
+        <v>189</v>
+      </c>
+      <c r="BF36" t="n">
+        <v>135</v>
+      </c>
+      <c r="BG36" t="n">
+        <v>119</v>
+      </c>
+      <c r="BH36" t="n">
         <v>108.7</v>
       </c>
-      <c r="BE36" t="n">
+      <c r="BI36" t="n">
         <v>197.8</v>
       </c>
-      <c r="BF36" t="n">
+      <c r="BJ36" t="n">
         <v>38.3</v>
       </c>
-      <c r="BG36" t="n">
+      <c r="BK36" t="n">
         <v>103</v>
       </c>
-      <c r="BH36" t="n">
-        <v>254</v>
-      </c>
-      <c r="BI36" t="n">
-        <v>189</v>
-      </c>
-      <c r="BJ36" t="n">
+      <c r="BL36" t="n">
         <v>222</v>
       </c>
     </row>
@@ -7461,24 +7681,30 @@
         <v>-103.3877865</v>
       </c>
       <c r="BD37" t="n">
+        <v>154</v>
+      </c>
+      <c r="BE37" t="n">
+        <v>98</v>
+      </c>
+      <c r="BF37" t="n">
+        <v>76</v>
+      </c>
+      <c r="BG37" t="n">
+        <v>78</v>
+      </c>
+      <c r="BH37" t="n">
         <v>62.7</v>
       </c>
-      <c r="BE37" t="n">
+      <c r="BI37" t="n">
         <v>86.8</v>
       </c>
-      <c r="BF37" t="n">
+      <c r="BJ37" t="n">
         <v>56.3</v>
       </c>
-      <c r="BG37" t="n">
+      <c r="BK37" t="n">
         <v>98.3</v>
       </c>
-      <c r="BH37" t="n">
-        <v>154</v>
-      </c>
-      <c r="BI37" t="n">
-        <v>98</v>
-      </c>
-      <c r="BJ37" t="n">
+      <c r="BL37" t="n">
         <v>158.9</v>
       </c>
     </row>
@@ -7649,24 +7875,30 @@
         <v>-103.7406</v>
       </c>
       <c r="BD38" t="n">
+        <v>88</v>
+      </c>
+      <c r="BE38" t="n">
+        <v>57</v>
+      </c>
+      <c r="BF38" t="n">
+        <v>47</v>
+      </c>
+      <c r="BG38" t="n">
+        <v>41</v>
+      </c>
+      <c r="BH38" t="n">
         <v>113.2</v>
       </c>
-      <c r="BE38" t="n">
+      <c r="BI38" t="n">
         <v>130.8</v>
       </c>
-      <c r="BF38" t="n">
+      <c r="BJ38" t="n">
         <v>79.40000000000001</v>
       </c>
-      <c r="BG38" t="n">
+      <c r="BK38" t="n">
         <v>170.3</v>
       </c>
-      <c r="BH38" t="n">
-        <v>88</v>
-      </c>
-      <c r="BI38" t="n">
-        <v>57</v>
-      </c>
-      <c r="BJ38" t="n">
+      <c r="BL38" t="n">
         <v>107.6</v>
       </c>
     </row>
@@ -7837,24 +8069,30 @@
         <v>-102.1830278</v>
       </c>
       <c r="BD39" t="n">
+        <v>746</v>
+      </c>
+      <c r="BE39" t="n">
+        <v>477</v>
+      </c>
+      <c r="BF39" t="n">
+        <v>424</v>
+      </c>
+      <c r="BG39" t="n">
+        <v>322</v>
+      </c>
+      <c r="BH39" t="n">
         <v>62.5</v>
       </c>
-      <c r="BE39" t="n">
+      <c r="BI39" t="n">
         <v>109.4</v>
       </c>
-      <c r="BF39" t="n">
+      <c r="BJ39" t="n">
         <v>70.5</v>
       </c>
-      <c r="BG39" t="n">
+      <c r="BK39" t="n">
         <v>132.3</v>
       </c>
-      <c r="BH39" t="n">
-        <v>746</v>
-      </c>
-      <c r="BI39" t="n">
-        <v>477</v>
-      </c>
-      <c r="BJ39" t="n">
+      <c r="BL39" t="n">
         <v>147.8</v>
       </c>
     </row>
@@ -8023,24 +8261,30 @@
         <v>-104.050605</v>
       </c>
       <c r="BD40" t="n">
+        <v>116</v>
+      </c>
+      <c r="BE40" t="n">
+        <v>76</v>
+      </c>
+      <c r="BF40" t="n">
+        <v>63</v>
+      </c>
+      <c r="BG40" t="n">
+        <v>53</v>
+      </c>
+      <c r="BH40" t="n">
         <v>50.3</v>
       </c>
-      <c r="BE40" t="n">
+      <c r="BI40" t="n">
         <v>91.2</v>
       </c>
-      <c r="BF40" t="n">
+      <c r="BJ40" t="n">
         <v>70.09999999999999</v>
       </c>
-      <c r="BG40" t="n">
+      <c r="BK40" t="n">
         <v>114.5</v>
       </c>
-      <c r="BH40" t="n">
-        <v>116</v>
-      </c>
-      <c r="BI40" t="n">
-        <v>76</v>
-      </c>
-      <c r="BJ40" t="n">
+      <c r="BL40" t="n">
         <v>143.9</v>
       </c>
     </row>
@@ -8211,24 +8455,30 @@
         <v>-103.4101899</v>
       </c>
       <c r="BD41" t="n">
+        <v>246</v>
+      </c>
+      <c r="BE41" t="n">
+        <v>152</v>
+      </c>
+      <c r="BF41" t="n">
+        <v>127</v>
+      </c>
+      <c r="BG41" t="n">
+        <v>119</v>
+      </c>
+      <c r="BH41" t="n">
         <v>91.8</v>
       </c>
-      <c r="BE41" t="n">
+      <c r="BI41" t="n">
         <v>144.7</v>
       </c>
-      <c r="BF41" t="n">
+      <c r="BJ41" t="n">
         <v>75.2</v>
       </c>
-      <c r="BG41" t="n">
+      <c r="BK41" t="n">
         <v>99.09999999999999</v>
       </c>
-      <c r="BH41" t="n">
-        <v>246</v>
-      </c>
-      <c r="BI41" t="n">
-        <v>152</v>
-      </c>
-      <c r="BJ41" t="n">
+      <c r="BL41" t="n">
         <v>143.7</v>
       </c>
     </row>
@@ -8397,24 +8647,30 @@
         <v>-104.8165356</v>
       </c>
       <c r="BD42" t="n">
+        <v>79</v>
+      </c>
+      <c r="BE42" t="n">
+        <v>45</v>
+      </c>
+      <c r="BF42" t="n">
+        <v>39</v>
+      </c>
+      <c r="BG42" t="n">
+        <v>40</v>
+      </c>
+      <c r="BH42" t="n">
         <v>39.9</v>
       </c>
-      <c r="BE42" t="n">
+      <c r="BI42" t="n">
         <v>87.90000000000001</v>
       </c>
-      <c r="BF42" t="n">
+      <c r="BJ42" t="n">
         <v>31.9</v>
       </c>
-      <c r="BG42" t="n">
+      <c r="BK42" t="n">
         <v>55.9</v>
       </c>
-      <c r="BH42" t="n">
-        <v>79</v>
-      </c>
-      <c r="BI42" t="n">
-        <v>45</v>
-      </c>
-      <c r="BJ42" t="n">
+      <c r="BL42" t="n">
         <v>153.5</v>
       </c>
     </row>
@@ -8585,24 +8841,30 @@
         <v>-104.013396</v>
       </c>
       <c r="BD43" t="n">
+        <v>81</v>
+      </c>
+      <c r="BE43" t="n">
+        <v>57</v>
+      </c>
+      <c r="BF43" t="n">
+        <v>34</v>
+      </c>
+      <c r="BG43" t="n">
+        <v>47</v>
+      </c>
+      <c r="BH43" t="n">
         <v>95.09999999999999</v>
       </c>
-      <c r="BE43" t="n">
+      <c r="BI43" t="n">
         <v>174</v>
       </c>
-      <c r="BF43" t="n">
+      <c r="BJ43" t="n">
         <v>52.5</v>
       </c>
-      <c r="BG43" t="n">
+      <c r="BK43" t="n">
         <v>109.8</v>
       </c>
-      <c r="BH43" t="n">
-        <v>81</v>
-      </c>
-      <c r="BI43" t="n">
-        <v>57</v>
-      </c>
-      <c r="BJ43" t="n">
+      <c r="BL43" t="n">
         <v>154.9</v>
       </c>
     </row>
@@ -8771,24 +9033,30 @@
         <v>-102.9836336</v>
       </c>
       <c r="BD44" t="n">
+        <v>98</v>
+      </c>
+      <c r="BE44" t="n">
+        <v>67</v>
+      </c>
+      <c r="BF44" t="n">
+        <v>60</v>
+      </c>
+      <c r="BG44" t="n">
+        <v>38</v>
+      </c>
+      <c r="BH44" t="n">
         <v>45.9</v>
       </c>
-      <c r="BE44" t="n">
+      <c r="BI44" t="n">
         <v>55</v>
       </c>
-      <c r="BF44" t="n">
+      <c r="BJ44" t="n">
         <v>78.5</v>
       </c>
-      <c r="BG44" t="n">
+      <c r="BK44" t="n">
         <v>99.40000000000001</v>
       </c>
-      <c r="BH44" t="n">
-        <v>98</v>
-      </c>
-      <c r="BI44" t="n">
-        <v>67</v>
-      </c>
-      <c r="BJ44" t="n">
+      <c r="BL44" t="n">
         <v>161.2</v>
       </c>
     </row>
@@ -8959,24 +9227,30 @@
         <v>-102.0008013</v>
       </c>
       <c r="BD45" t="n">
+        <v>207</v>
+      </c>
+      <c r="BE45" t="n">
+        <v>131</v>
+      </c>
+      <c r="BF45" t="n">
+        <v>105</v>
+      </c>
+      <c r="BG45" t="n">
+        <v>102</v>
+      </c>
+      <c r="BH45" t="n">
         <v>63.4</v>
       </c>
-      <c r="BE45" t="n">
+      <c r="BI45" t="n">
         <v>89.90000000000001</v>
       </c>
-      <c r="BF45" t="n">
+      <c r="BJ45" t="n">
         <v>45.1</v>
       </c>
-      <c r="BG45" t="n">
+      <c r="BK45" t="n">
         <v>84</v>
       </c>
-      <c r="BH45" t="n">
-        <v>207</v>
-      </c>
-      <c r="BI45" t="n">
-        <v>131</v>
-      </c>
-      <c r="BJ45" t="n">
+      <c r="BL45" t="n">
         <v>109.7</v>
       </c>
     </row>
@@ -9147,24 +9421,30 @@
         <v>-104.7327378</v>
       </c>
       <c r="BD46" t="n">
+        <v>197</v>
+      </c>
+      <c r="BE46" t="n">
+        <v>128</v>
+      </c>
+      <c r="BF46" t="n">
+        <v>101</v>
+      </c>
+      <c r="BG46" t="n">
+        <v>96</v>
+      </c>
+      <c r="BH46" t="n">
         <v>31.3</v>
       </c>
-      <c r="BE46" t="n">
+      <c r="BI46" t="n">
         <v>66.90000000000001</v>
       </c>
-      <c r="BF46" t="n">
+      <c r="BJ46" t="n">
         <v>84.8</v>
       </c>
-      <c r="BG46" t="n">
+      <c r="BK46" t="n">
         <v>125</v>
       </c>
-      <c r="BH46" t="n">
-        <v>197</v>
-      </c>
-      <c r="BI46" t="n">
-        <v>128</v>
-      </c>
-      <c r="BJ46" t="n">
+      <c r="BL46" t="n">
         <v>179.1</v>
       </c>
     </row>
@@ -9335,24 +9615,30 @@
         <v>-102.8871612</v>
       </c>
       <c r="BD47" t="n">
+        <v>142</v>
+      </c>
+      <c r="BE47" t="n">
+        <v>97</v>
+      </c>
+      <c r="BF47" t="n">
+        <v>88</v>
+      </c>
+      <c r="BG47" t="n">
+        <v>54</v>
+      </c>
+      <c r="BH47" t="n">
         <v>90.09999999999999</v>
       </c>
-      <c r="BE47" t="n">
+      <c r="BI47" t="n">
         <v>137.3</v>
       </c>
-      <c r="BF47" t="n">
+      <c r="BJ47" t="n">
         <v>45.4</v>
       </c>
-      <c r="BG47" t="n">
+      <c r="BK47" t="n">
         <v>65.09999999999999</v>
       </c>
-      <c r="BH47" t="n">
-        <v>142</v>
-      </c>
-      <c r="BI47" t="n">
-        <v>97</v>
-      </c>
-      <c r="BJ47" t="n">
+      <c r="BL47" t="n">
         <v>218</v>
       </c>
     </row>
@@ -9523,24 +9809,30 @@
         <v>-105.1509531</v>
       </c>
       <c r="BD48" t="n">
+        <v>429</v>
+      </c>
+      <c r="BE48" t="n">
+        <v>286</v>
+      </c>
+      <c r="BF48" t="n">
+        <v>218</v>
+      </c>
+      <c r="BG48" t="n">
+        <v>211</v>
+      </c>
+      <c r="BH48" t="n">
         <v>57.5</v>
       </c>
-      <c r="BE48" t="n">
+      <c r="BI48" t="n">
         <v>112.9</v>
       </c>
-      <c r="BF48" t="n">
+      <c r="BJ48" t="n">
         <v>56</v>
       </c>
-      <c r="BG48" t="n">
+      <c r="BK48" t="n">
         <v>93.3</v>
       </c>
-      <c r="BH48" t="n">
-        <v>429</v>
-      </c>
-      <c r="BI48" t="n">
-        <v>286</v>
-      </c>
-      <c r="BJ48" t="n">
+      <c r="BL48" t="n">
         <v>133.1</v>
       </c>
     </row>
@@ -9711,24 +10003,30 @@
         <v>-104.0478154</v>
       </c>
       <c r="BD49" t="n">
+        <v>80</v>
+      </c>
+      <c r="BE49" t="n">
+        <v>58</v>
+      </c>
+      <c r="BF49" t="n">
+        <v>44</v>
+      </c>
+      <c r="BG49" t="n">
+        <v>36</v>
+      </c>
+      <c r="BH49" t="n">
         <v>41.5</v>
       </c>
-      <c r="BE49" t="n">
+      <c r="BI49" t="n">
         <v>68.09999999999999</v>
       </c>
-      <c r="BF49" t="n">
+      <c r="BJ49" t="n">
         <v>51.2</v>
       </c>
-      <c r="BG49" t="n">
+      <c r="BK49" t="n">
         <v>125.6</v>
       </c>
-      <c r="BH49" t="n">
-        <v>80</v>
-      </c>
-      <c r="BI49" t="n">
-        <v>58</v>
-      </c>
-      <c r="BJ49" t="n">
+      <c r="BL49" t="n">
         <v>174.3</v>
       </c>
     </row>
@@ -9897,24 +10195,30 @@
         <v>-103.9923066</v>
       </c>
       <c r="BD50" t="n">
+        <v>165</v>
+      </c>
+      <c r="BE50" t="n">
+        <v>104</v>
+      </c>
+      <c r="BF50" t="n">
+        <v>88</v>
+      </c>
+      <c r="BG50" t="n">
+        <v>77</v>
+      </c>
+      <c r="BH50" t="n">
         <v>77.5</v>
       </c>
-      <c r="BE50" t="n">
+      <c r="BI50" t="n">
         <v>84.3</v>
       </c>
-      <c r="BF50" t="n">
+      <c r="BJ50" t="n">
         <v>56.1</v>
       </c>
-      <c r="BG50" t="n">
+      <c r="BK50" t="n">
         <v>102.7</v>
       </c>
-      <c r="BH50" t="n">
-        <v>165</v>
-      </c>
-      <c r="BI50" t="n">
-        <v>104</v>
-      </c>
-      <c r="BJ50" t="n">
+      <c r="BL50" t="n">
         <v>182.5</v>
       </c>
     </row>
@@ -10083,24 +10387,30 @@
         <v>-102.520115</v>
       </c>
       <c r="BD51" t="n">
+        <v>613</v>
+      </c>
+      <c r="BE51" t="n">
+        <v>371</v>
+      </c>
+      <c r="BF51" t="n">
+        <v>366</v>
+      </c>
+      <c r="BG51" t="n">
+        <v>247</v>
+      </c>
+      <c r="BH51" t="n">
         <v>61.6</v>
       </c>
-      <c r="BE51" t="n">
+      <c r="BI51" t="n">
         <v>130</v>
       </c>
-      <c r="BF51" t="n">
+      <c r="BJ51" t="n">
         <v>73.09999999999999</v>
       </c>
-      <c r="BG51" t="n">
+      <c r="BK51" t="n">
         <v>115.9</v>
       </c>
-      <c r="BH51" t="n">
-        <v>613</v>
-      </c>
-      <c r="BI51" t="n">
-        <v>371</v>
-      </c>
-      <c r="BJ51" t="n">
+      <c r="BL51" t="n">
         <v>153.4</v>
       </c>
     </row>
@@ -10271,24 +10581,30 @@
         <v>-104.9524361</v>
       </c>
       <c r="BD52" t="n">
+        <v>154</v>
+      </c>
+      <c r="BE52" t="n">
+        <v>95</v>
+      </c>
+      <c r="BF52" t="n">
+        <v>88</v>
+      </c>
+      <c r="BG52" t="n">
+        <v>66</v>
+      </c>
+      <c r="BH52" t="n">
         <v>35.5</v>
       </c>
-      <c r="BE52" t="n">
+      <c r="BI52" t="n">
         <v>77.8</v>
       </c>
-      <c r="BF52" t="n">
+      <c r="BJ52" t="n">
         <v>15.6</v>
       </c>
-      <c r="BG52" t="n">
+      <c r="BK52" t="n">
         <v>41.1</v>
       </c>
-      <c r="BH52" t="n">
-        <v>154</v>
-      </c>
-      <c r="BI52" t="n">
-        <v>95</v>
-      </c>
-      <c r="BJ52" t="n">
+      <c r="BL52" t="n">
         <v>103.7</v>
       </c>
     </row>
@@ -10459,24 +10775,30 @@
         <v>-105.220306</v>
       </c>
       <c r="BD53" t="n">
+        <v>3242</v>
+      </c>
+      <c r="BE53" t="n">
+        <v>2090</v>
+      </c>
+      <c r="BF53" t="n">
+        <v>1148</v>
+      </c>
+      <c r="BG53" t="n">
+        <v>2094</v>
+      </c>
+      <c r="BH53" t="n">
         <v>56.4</v>
       </c>
-      <c r="BE53" t="n">
+      <c r="BI53" t="n">
         <v>164.1</v>
       </c>
-      <c r="BF53" t="n">
+      <c r="BJ53" t="n">
         <v>60.4</v>
       </c>
-      <c r="BG53" t="n">
+      <c r="BK53" t="n">
         <v>125.3</v>
       </c>
-      <c r="BH53" t="n">
-        <v>3242</v>
-      </c>
-      <c r="BI53" t="n">
-        <v>2090</v>
-      </c>
-      <c r="BJ53" t="n">
+      <c r="BL53" t="n">
         <v>113</v>
       </c>
     </row>
@@ -10647,24 +10969,30 @@
         <v>-103.0810204</v>
       </c>
       <c r="BD54" t="n">
+        <v>201</v>
+      </c>
+      <c r="BE54" t="n">
+        <v>126</v>
+      </c>
+      <c r="BF54" t="n">
+        <v>72</v>
+      </c>
+      <c r="BG54" t="n">
+        <v>129</v>
+      </c>
+      <c r="BH54" t="n">
         <v>61.6</v>
       </c>
-      <c r="BE54" t="n">
+      <c r="BI54" t="n">
         <v>122.3</v>
       </c>
-      <c r="BF54" t="n">
+      <c r="BJ54" t="n">
         <v>61.5</v>
       </c>
-      <c r="BG54" t="n">
+      <c r="BK54" t="n">
         <v>110.8</v>
       </c>
-      <c r="BH54" t="n">
-        <v>201</v>
-      </c>
-      <c r="BI54" t="n">
-        <v>126</v>
-      </c>
-      <c r="BJ54" t="n">
+      <c r="BL54" t="n">
         <v>143.6</v>
       </c>
     </row>
@@ -10833,24 +11161,30 @@
         <v>-102.7074318</v>
       </c>
       <c r="BD55" t="n">
+        <v>55</v>
+      </c>
+      <c r="BE55" t="n">
+        <v>34</v>
+      </c>
+      <c r="BF55" t="n">
+        <v>27</v>
+      </c>
+      <c r="BG55" t="n">
+        <v>28</v>
+      </c>
+      <c r="BH55" t="n">
         <v>66.09999999999999</v>
       </c>
-      <c r="BE55" t="n">
+      <c r="BI55" t="n">
         <v>89.90000000000001</v>
       </c>
-      <c r="BF55" t="n">
+      <c r="BJ55" t="n">
         <v>39.5</v>
       </c>
-      <c r="BG55" t="n">
+      <c r="BK55" t="n">
         <v>46.5</v>
       </c>
-      <c r="BH55" t="n">
-        <v>55</v>
-      </c>
-      <c r="BI55" t="n">
-        <v>34</v>
-      </c>
-      <c r="BJ55" t="n">
+      <c r="BL55" t="n">
         <v>121.4</v>
       </c>
     </row>
@@ -11021,24 +11355,30 @@
         <v>-101.593513</v>
       </c>
       <c r="BD56" t="n">
+        <v>393</v>
+      </c>
+      <c r="BE56" t="n">
+        <v>251</v>
+      </c>
+      <c r="BF56" t="n">
+        <v>240</v>
+      </c>
+      <c r="BG56" t="n">
+        <v>153</v>
+      </c>
+      <c r="BH56" t="n">
         <v>63.8</v>
       </c>
-      <c r="BE56" t="n">
+      <c r="BI56" t="n">
         <v>107.6</v>
       </c>
-      <c r="BF56" t="n">
+      <c r="BJ56" t="n">
         <v>85.40000000000001</v>
       </c>
-      <c r="BG56" t="n">
+      <c r="BK56" t="n">
         <v>120.6</v>
       </c>
-      <c r="BH56" t="n">
-        <v>393</v>
-      </c>
-      <c r="BI56" t="n">
-        <v>251</v>
-      </c>
-      <c r="BJ56" t="n">
+      <c r="BL56" t="n">
         <v>118.6</v>
       </c>
     </row>
@@ -11209,24 +11549,30 @@
         <v>-104.3183402</v>
       </c>
       <c r="BD57" t="n">
+        <v>1003</v>
+      </c>
+      <c r="BE57" t="n">
+        <v>673</v>
+      </c>
+      <c r="BF57" t="n">
+        <v>379</v>
+      </c>
+      <c r="BG57" t="n">
+        <v>624</v>
+      </c>
+      <c r="BH57" t="n">
         <v>51.9</v>
       </c>
-      <c r="BE57" t="n">
+      <c r="BI57" t="n">
         <v>146.4</v>
       </c>
-      <c r="BF57" t="n">
+      <c r="BJ57" t="n">
         <v>50.7</v>
       </c>
-      <c r="BG57" t="n">
+      <c r="BK57" t="n">
         <v>126</v>
       </c>
-      <c r="BH57" t="n">
-        <v>1003</v>
-      </c>
-      <c r="BI57" t="n">
-        <v>673</v>
-      </c>
-      <c r="BJ57" t="n">
+      <c r="BL57" t="n">
         <v>161.8</v>
       </c>
     </row>
@@ -11397,24 +11743,30 @@
         <v>-104.8072221</v>
       </c>
       <c r="BD58" t="n">
+        <v>334</v>
+      </c>
+      <c r="BE58" t="n">
+        <v>226</v>
+      </c>
+      <c r="BF58" t="n">
+        <v>151</v>
+      </c>
+      <c r="BG58" t="n">
+        <v>183</v>
+      </c>
+      <c r="BH58" t="n">
         <v>39.5</v>
       </c>
-      <c r="BE58" t="n">
+      <c r="BI58" t="n">
         <v>80.90000000000001</v>
       </c>
-      <c r="BF58" t="n">
+      <c r="BJ58" t="n">
         <v>68.2</v>
       </c>
-      <c r="BG58" t="n">
+      <c r="BK58" t="n">
         <v>119.2</v>
       </c>
-      <c r="BH58" t="n">
-        <v>334</v>
-      </c>
-      <c r="BI58" t="n">
-        <v>226</v>
-      </c>
-      <c r="BJ58" t="n">
+      <c r="BL58" t="n">
         <v>159.4</v>
       </c>
     </row>
@@ -11585,24 +11937,30 @@
         <v>-103.7105199</v>
       </c>
       <c r="BD59" t="n">
+        <v>227</v>
+      </c>
+      <c r="BE59" t="n">
+        <v>156</v>
+      </c>
+      <c r="BF59" t="n">
+        <v>135</v>
+      </c>
+      <c r="BG59" t="n">
+        <v>92</v>
+      </c>
+      <c r="BH59" t="n">
         <v>40.6</v>
       </c>
-      <c r="BE59" t="n">
+      <c r="BI59" t="n">
         <v>116.1</v>
       </c>
-      <c r="BF59" t="n">
+      <c r="BJ59" t="n">
         <v>93.59999999999999</v>
       </c>
-      <c r="BG59" t="n">
+      <c r="BK59" t="n">
         <v>142.1</v>
       </c>
-      <c r="BH59" t="n">
-        <v>227</v>
-      </c>
-      <c r="BI59" t="n">
-        <v>156</v>
-      </c>
-      <c r="BJ59" t="n">
+      <c r="BL59" t="n">
         <v>147.4</v>
       </c>
     </row>
@@ -11773,24 +12131,30 @@
         <v>-104.115854</v>
       </c>
       <c r="BD60" t="n">
+        <v>240</v>
+      </c>
+      <c r="BE60" t="n">
+        <v>147</v>
+      </c>
+      <c r="BF60" t="n">
+        <v>108</v>
+      </c>
+      <c r="BG60" t="n">
+        <v>132</v>
+      </c>
+      <c r="BH60" t="n">
         <v>21.4</v>
       </c>
-      <c r="BE60" t="n">
+      <c r="BI60" t="n">
         <v>61.6</v>
       </c>
-      <c r="BF60" t="n">
+      <c r="BJ60" t="n">
         <v>69.7</v>
       </c>
-      <c r="BG60" t="n">
+      <c r="BK60" t="n">
         <v>104.7</v>
       </c>
-      <c r="BH60" t="n">
-        <v>240</v>
-      </c>
-      <c r="BI60" t="n">
-        <v>147</v>
-      </c>
-      <c r="BJ60" t="n">
+      <c r="BL60" t="n">
         <v>111.4</v>
       </c>
     </row>
@@ -11961,24 +12325,30 @@
         <v>-102.0261866</v>
       </c>
       <c r="BD61" t="n">
+        <v>110</v>
+      </c>
+      <c r="BE61" t="n">
+        <v>66</v>
+      </c>
+      <c r="BF61" t="n">
+        <v>65</v>
+      </c>
+      <c r="BG61" t="n">
+        <v>45</v>
+      </c>
+      <c r="BH61" t="n">
         <v>35.9</v>
       </c>
-      <c r="BE61" t="n">
+      <c r="BI61" t="n">
         <v>66.3</v>
       </c>
-      <c r="BF61" t="n">
+      <c r="BJ61" t="n">
         <v>82.3</v>
       </c>
-      <c r="BG61" t="n">
+      <c r="BK61" t="n">
         <v>114.4</v>
       </c>
-      <c r="BH61" t="n">
-        <v>110</v>
-      </c>
-      <c r="BI61" t="n">
-        <v>66</v>
-      </c>
-      <c r="BJ61" t="n">
+      <c r="BL61" t="n">
         <v>137.1</v>
       </c>
     </row>
@@ -12147,24 +12517,30 @@
         <v>-103.9299109</v>
       </c>
       <c r="BD62" t="n">
+        <v>101</v>
+      </c>
+      <c r="BE62" t="n">
+        <v>69</v>
+      </c>
+      <c r="BF62" t="n">
+        <v>65</v>
+      </c>
+      <c r="BG62" t="n">
+        <v>36</v>
+      </c>
+      <c r="BH62" t="n">
         <v>24.5</v>
       </c>
-      <c r="BE62" t="n">
+      <c r="BI62" t="n">
         <v>38.8</v>
       </c>
-      <c r="BF62" t="n">
+      <c r="BJ62" t="n">
         <v>54</v>
       </c>
-      <c r="BG62" t="n">
+      <c r="BK62" t="n">
         <v>70.5</v>
       </c>
-      <c r="BH62" t="n">
-        <v>101</v>
-      </c>
-      <c r="BI62" t="n">
-        <v>69</v>
-      </c>
-      <c r="BJ62" t="n">
+      <c r="BL62" t="n">
         <v>102.1</v>
       </c>
     </row>
@@ -12335,24 +12711,30 @@
         <v>-103.8815785</v>
       </c>
       <c r="BD63" t="n">
+        <v>86</v>
+      </c>
+      <c r="BE63" t="n">
+        <v>50</v>
+      </c>
+      <c r="BF63" t="n">
+        <v>60</v>
+      </c>
+      <c r="BG63" t="n">
+        <v>26</v>
+      </c>
+      <c r="BH63" t="n">
         <v>31.8</v>
       </c>
-      <c r="BE63" t="n">
+      <c r="BI63" t="n">
         <v>31.8</v>
       </c>
-      <c r="BF63" t="n">
+      <c r="BJ63" t="n">
         <v>111.2</v>
       </c>
-      <c r="BG63" t="n">
+      <c r="BK63" t="n">
         <v>131.4</v>
       </c>
-      <c r="BH63" t="n">
-        <v>86</v>
-      </c>
-      <c r="BI63" t="n">
-        <v>50</v>
-      </c>
-      <c r="BJ63" t="n">
+      <c r="BL63" t="n">
         <v>137.4</v>
       </c>
     </row>
@@ -12521,24 +12903,30 @@
         <v>-102.6798646</v>
       </c>
       <c r="BD64" t="n">
+        <v>73</v>
+      </c>
+      <c r="BE64" t="n">
+        <v>44</v>
+      </c>
+      <c r="BF64" t="n">
+        <v>37</v>
+      </c>
+      <c r="BG64" t="n">
+        <v>36</v>
+      </c>
+      <c r="BH64" t="n">
         <v>23.8</v>
       </c>
-      <c r="BE64" t="n">
+      <c r="BI64" t="n">
         <v>53.4</v>
       </c>
-      <c r="BF64" t="n">
+      <c r="BJ64" t="n">
         <v>40.1</v>
       </c>
-      <c r="BG64" t="n">
+      <c r="BK64" t="n">
         <v>48.2</v>
       </c>
-      <c r="BH64" t="n">
-        <v>73</v>
-      </c>
-      <c r="BI64" t="n">
-        <v>44</v>
-      </c>
-      <c r="BJ64" t="n">
+      <c r="BL64" t="n">
         <v>108.7</v>
       </c>
     </row>
@@ -12707,24 +13095,30 @@
         <v>-104.1956497</v>
       </c>
       <c r="BD65" t="n">
+        <v>62</v>
+      </c>
+      <c r="BE65" t="n">
+        <v>42</v>
+      </c>
+      <c r="BF65" t="n">
+        <v>25</v>
+      </c>
+      <c r="BG65" t="n">
+        <v>37</v>
+      </c>
+      <c r="BH65" t="n">
         <v>42.7</v>
       </c>
-      <c r="BE65" t="n">
+      <c r="BI65" t="n">
         <v>66.5</v>
       </c>
-      <c r="BF65" t="n">
+      <c r="BJ65" t="n">
         <v>16.5</v>
       </c>
-      <c r="BG65" t="n">
+      <c r="BK65" t="n">
         <v>99</v>
       </c>
-      <c r="BH65" t="n">
-        <v>62</v>
-      </c>
-      <c r="BI65" t="n">
-        <v>42</v>
-      </c>
-      <c r="BJ65" t="n">
+      <c r="BL65" t="n">
         <v>183.3</v>
       </c>
     </row>
@@ -12893,24 +13287,30 @@
         <v>-103.7761059</v>
       </c>
       <c r="BD66" t="n">
+        <v>285</v>
+      </c>
+      <c r="BE66" t="n">
+        <v>174</v>
+      </c>
+      <c r="BF66" t="n">
+        <v>136</v>
+      </c>
+      <c r="BG66" t="n">
+        <v>149</v>
+      </c>
+      <c r="BH66" t="n">
         <v>57.5</v>
       </c>
-      <c r="BE66" t="n">
+      <c r="BI66" t="n">
         <v>154.5</v>
       </c>
-      <c r="BF66" t="n">
+      <c r="BJ66" t="n">
         <v>72</v>
       </c>
-      <c r="BG66" t="n">
+      <c r="BK66" t="n">
         <v>135.7</v>
       </c>
-      <c r="BH66" t="n">
-        <v>285</v>
-      </c>
-      <c r="BI66" t="n">
-        <v>174</v>
-      </c>
-      <c r="BJ66" t="n">
+      <c r="BL66" t="n">
         <v>127.6</v>
       </c>
     </row>
@@ -13081,24 +13481,30 @@
         <v>-102.5834854</v>
       </c>
       <c r="BD67" t="n">
+        <v>277</v>
+      </c>
+      <c r="BE67" t="n">
+        <v>151</v>
+      </c>
+      <c r="BF67" t="n">
+        <v>116</v>
+      </c>
+      <c r="BG67" t="n">
+        <v>161</v>
+      </c>
+      <c r="BH67" t="n">
         <v>67.40000000000001</v>
       </c>
-      <c r="BE67" t="n">
+      <c r="BI67" t="n">
         <v>116.6</v>
       </c>
-      <c r="BF67" t="n">
+      <c r="BJ67" t="n">
         <v>40.5</v>
       </c>
-      <c r="BG67" t="n">
+      <c r="BK67" t="n">
         <v>88.3</v>
       </c>
-      <c r="BH67" t="n">
-        <v>277</v>
-      </c>
-      <c r="BI67" t="n">
-        <v>151</v>
-      </c>
-      <c r="BJ67" t="n">
+      <c r="BL67" t="n">
         <v>125.5</v>
       </c>
     </row>
@@ -13267,24 +13673,30 @@
         <v>-103.6088957</v>
       </c>
       <c r="BD68" t="n">
+        <v>593</v>
+      </c>
+      <c r="BE68" t="n">
+        <v>385</v>
+      </c>
+      <c r="BF68" t="n">
+        <v>306</v>
+      </c>
+      <c r="BG68" t="n">
+        <v>287</v>
+      </c>
+      <c r="BH68" t="n">
         <v>89.8</v>
       </c>
-      <c r="BE68" t="n">
+      <c r="BI68" t="n">
         <v>158.8</v>
       </c>
-      <c r="BF68" t="n">
+      <c r="BJ68" t="n">
         <v>78.90000000000001</v>
       </c>
-      <c r="BG68" t="n">
+      <c r="BK68" t="n">
         <v>124.4</v>
       </c>
-      <c r="BH68" t="n">
-        <v>593</v>
-      </c>
-      <c r="BI68" t="n">
-        <v>385</v>
-      </c>
-      <c r="BJ68" t="n">
+      <c r="BL68" t="n">
         <v>167.5</v>
       </c>
     </row>
@@ -13453,24 +13865,30 @@
         <v>-103.9822552</v>
       </c>
       <c r="BD69" t="n">
+        <v>252</v>
+      </c>
+      <c r="BE69" t="n">
+        <v>154</v>
+      </c>
+      <c r="BF69" t="n">
+        <v>127</v>
+      </c>
+      <c r="BG69" t="n">
+        <v>125</v>
+      </c>
+      <c r="BH69" t="n">
         <v>59.8</v>
       </c>
-      <c r="BE69" t="n">
+      <c r="BI69" t="n">
         <v>98.09999999999999</v>
       </c>
-      <c r="BF69" t="n">
+      <c r="BJ69" t="n">
         <v>54.3</v>
       </c>
-      <c r="BG69" t="n">
+      <c r="BK69" t="n">
         <v>104.8</v>
       </c>
-      <c r="BH69" t="n">
-        <v>252</v>
-      </c>
-      <c r="BI69" t="n">
-        <v>154</v>
-      </c>
-      <c r="BJ69" t="n">
+      <c r="BL69" t="n">
         <v>151.4</v>
       </c>
     </row>
@@ -13639,24 +14057,30 @@
         <v>-103.0983817</v>
       </c>
       <c r="BD70" t="n">
+        <v>290</v>
+      </c>
+      <c r="BE70" t="n">
+        <v>195</v>
+      </c>
+      <c r="BF70" t="n">
+        <v>183</v>
+      </c>
+      <c r="BG70" t="n">
+        <v>106</v>
+      </c>
+      <c r="BH70" t="n">
         <v>72.2</v>
       </c>
-      <c r="BE70" t="n">
+      <c r="BI70" t="n">
         <v>113</v>
       </c>
-      <c r="BF70" t="n">
+      <c r="BJ70" t="n">
         <v>52.8</v>
       </c>
-      <c r="BG70" t="n">
+      <c r="BK70" t="n">
         <v>98.8</v>
       </c>
-      <c r="BH70" t="n">
-        <v>290</v>
-      </c>
-      <c r="BI70" t="n">
-        <v>195</v>
-      </c>
-      <c r="BJ70" t="n">
+      <c r="BL70" t="n">
         <v>132.3</v>
       </c>
     </row>
@@ -13825,24 +14249,30 @@
         <v>-102.1748235</v>
       </c>
       <c r="BD71" t="n">
+        <v>286</v>
+      </c>
+      <c r="BE71" t="n">
+        <v>166</v>
+      </c>
+      <c r="BF71" t="n">
+        <v>197</v>
+      </c>
+      <c r="BG71" t="n">
+        <v>89</v>
+      </c>
+      <c r="BH71" t="n">
         <v>62.2</v>
       </c>
-      <c r="BE71" t="n">
+      <c r="BI71" t="n">
         <v>95.5</v>
       </c>
-      <c r="BF71" t="n">
+      <c r="BJ71" t="n">
         <v>50.5</v>
       </c>
-      <c r="BG71" t="n">
+      <c r="BK71" t="n">
         <v>71.90000000000001</v>
       </c>
-      <c r="BH71" t="n">
-        <v>286</v>
-      </c>
-      <c r="BI71" t="n">
-        <v>166</v>
-      </c>
-      <c r="BJ71" t="n">
+      <c r="BL71" t="n">
         <v>128.2</v>
       </c>
     </row>
@@ -14013,24 +14443,30 @@
         <v>-103.5931063</v>
       </c>
       <c r="BD72" t="n">
+        <v>452</v>
+      </c>
+      <c r="BE72" t="n">
+        <v>312</v>
+      </c>
+      <c r="BF72" t="n">
+        <v>262</v>
+      </c>
+      <c r="BG72" t="n">
+        <v>190</v>
+      </c>
+      <c r="BH72" t="n">
         <v>58.5</v>
       </c>
-      <c r="BE72" t="n">
+      <c r="BI72" t="n">
         <v>99.09999999999999</v>
       </c>
-      <c r="BF72" t="n">
+      <c r="BJ72" t="n">
         <v>94.59999999999999</v>
       </c>
-      <c r="BG72" t="n">
+      <c r="BK72" t="n">
         <v>140.4</v>
       </c>
-      <c r="BH72" t="n">
-        <v>452</v>
-      </c>
-      <c r="BI72" t="n">
-        <v>312</v>
-      </c>
-      <c r="BJ72" t="n">
+      <c r="BL72" t="n">
         <v>158.8</v>
       </c>
     </row>
@@ -14201,24 +14637,30 @@
         <v>-102.3641293</v>
       </c>
       <c r="BD73" t="n">
+        <v>586</v>
+      </c>
+      <c r="BE73" t="n">
+        <v>402</v>
+      </c>
+      <c r="BF73" t="n">
+        <v>385</v>
+      </c>
+      <c r="BG73" t="n">
+        <v>201</v>
+      </c>
+      <c r="BH73" t="n">
         <v>73.3</v>
       </c>
-      <c r="BE73" t="n">
+      <c r="BI73" t="n">
         <v>127.4</v>
       </c>
-      <c r="BF73" t="n">
+      <c r="BJ73" t="n">
         <v>91.90000000000001</v>
       </c>
-      <c r="BG73" t="n">
+      <c r="BK73" t="n">
         <v>124.4</v>
       </c>
-      <c r="BH73" t="n">
-        <v>586</v>
-      </c>
-      <c r="BI73" t="n">
-        <v>402</v>
-      </c>
-      <c r="BJ73" t="n">
+      <c r="BL73" t="n">
         <v>148.4</v>
       </c>
     </row>
@@ -14387,24 +14829,30 @@
         <v>-104.7633816</v>
       </c>
       <c r="BD74" t="n">
+        <v>225</v>
+      </c>
+      <c r="BE74" t="n">
+        <v>144</v>
+      </c>
+      <c r="BF74" t="n">
+        <v>110</v>
+      </c>
+      <c r="BG74" t="n">
+        <v>115</v>
+      </c>
+      <c r="BH74" t="n">
         <v>38.3</v>
       </c>
-      <c r="BE74" t="n">
+      <c r="BI74" t="n">
         <v>108.6</v>
       </c>
-      <c r="BF74" t="n">
+      <c r="BJ74" t="n">
         <v>42.7</v>
       </c>
-      <c r="BG74" t="n">
+      <c r="BK74" t="n">
         <v>83.59999999999999</v>
       </c>
-      <c r="BH74" t="n">
-        <v>225</v>
-      </c>
-      <c r="BI74" t="n">
-        <v>144</v>
-      </c>
-      <c r="BJ74" t="n">
+      <c r="BL74" t="n">
         <v>165</v>
       </c>
     </row>
@@ -14575,24 +15023,30 @@
         <v>-101.8199571</v>
       </c>
       <c r="BD75" t="n">
+        <v>2108</v>
+      </c>
+      <c r="BE75" t="n">
+        <v>1350</v>
+      </c>
+      <c r="BF75" t="n">
+        <v>1019</v>
+      </c>
+      <c r="BG75" t="n">
+        <v>1089</v>
+      </c>
+      <c r="BH75" t="n">
         <v>60.7</v>
       </c>
-      <c r="BE75" t="n">
+      <c r="BI75" t="n">
         <v>131.8</v>
       </c>
-      <c r="BF75" t="n">
+      <c r="BJ75" t="n">
         <v>72.7</v>
       </c>
-      <c r="BG75" t="n">
+      <c r="BK75" t="n">
         <v>133.3</v>
       </c>
-      <c r="BH75" t="n">
-        <v>2108</v>
-      </c>
-      <c r="BI75" t="n">
-        <v>1350</v>
-      </c>
-      <c r="BJ75" t="n">
+      <c r="BL75" t="n">
         <v>124</v>
       </c>
     </row>
@@ -14763,24 +15217,30 @@
         <v>-104.064661</v>
       </c>
       <c r="BD76" t="n">
+        <v>1107</v>
+      </c>
+      <c r="BE76" t="n">
+        <v>717</v>
+      </c>
+      <c r="BF76" t="n">
+        <v>545</v>
+      </c>
+      <c r="BG76" t="n">
+        <v>562</v>
+      </c>
+      <c r="BH76" t="n">
         <v>65.90000000000001</v>
       </c>
-      <c r="BE76" t="n">
+      <c r="BI76" t="n">
         <v>141</v>
       </c>
-      <c r="BF76" t="n">
+      <c r="BJ76" t="n">
         <v>53.8</v>
       </c>
-      <c r="BG76" t="n">
+      <c r="BK76" t="n">
         <v>111.8</v>
       </c>
-      <c r="BH76" t="n">
-        <v>1107</v>
-      </c>
-      <c r="BI76" t="n">
-        <v>717</v>
-      </c>
-      <c r="BJ76" t="n">
+      <c r="BL76" t="n">
         <v>198.4</v>
       </c>
     </row>
@@ -14951,24 +15411,30 @@
         <v>-103.510648</v>
       </c>
       <c r="BD77" t="n">
+        <v>1687</v>
+      </c>
+      <c r="BE77" t="n">
+        <v>1125</v>
+      </c>
+      <c r="BF77" t="n">
+        <v>896</v>
+      </c>
+      <c r="BG77" t="n">
+        <v>791</v>
+      </c>
+      <c r="BH77" t="n">
         <v>98.2</v>
       </c>
-      <c r="BE77" t="n">
+      <c r="BI77" t="n">
         <v>160.2</v>
       </c>
-      <c r="BF77" t="n">
+      <c r="BJ77" t="n">
         <v>71.40000000000001</v>
       </c>
-      <c r="BG77" t="n">
+      <c r="BK77" t="n">
         <v>112.8</v>
       </c>
-      <c r="BH77" t="n">
-        <v>1687</v>
-      </c>
-      <c r="BI77" t="n">
-        <v>1125</v>
-      </c>
-      <c r="BJ77" t="n">
+      <c r="BL77" t="n">
         <v>150.1</v>
       </c>
     </row>
@@ -15139,24 +15605,30 @@
         <v>-103.170067</v>
       </c>
       <c r="BD78" t="n">
+        <v>796</v>
+      </c>
+      <c r="BE78" t="n">
+        <v>506</v>
+      </c>
+      <c r="BF78" t="n">
+        <v>419</v>
+      </c>
+      <c r="BG78" t="n">
+        <v>376</v>
+      </c>
+      <c r="BH78" t="n">
         <v>90.8</v>
       </c>
-      <c r="BE78" t="n">
+      <c r="BI78" t="n">
         <v>167.6</v>
       </c>
-      <c r="BF78" t="n">
+      <c r="BJ78" t="n">
         <v>74.90000000000001</v>
       </c>
-      <c r="BG78" t="n">
+      <c r="BK78" t="n">
         <v>118.5</v>
       </c>
-      <c r="BH78" t="n">
-        <v>796</v>
-      </c>
-      <c r="BI78" t="n">
-        <v>506</v>
-      </c>
-      <c r="BJ78" t="n">
+      <c r="BL78" t="n">
         <v>227.7</v>
       </c>
     </row>
@@ -15327,24 +15799,30 @@
         <v>-103.4164682</v>
       </c>
       <c r="BD79" t="n">
+        <v>574</v>
+      </c>
+      <c r="BE79" t="n">
+        <v>381</v>
+      </c>
+      <c r="BF79" t="n">
+        <v>302</v>
+      </c>
+      <c r="BG79" t="n">
+        <v>272</v>
+      </c>
+      <c r="BH79" t="n">
         <v>106.3</v>
       </c>
-      <c r="BE79" t="n">
+      <c r="BI79" t="n">
         <v>205.9</v>
       </c>
-      <c r="BF79" t="n">
+      <c r="BJ79" t="n">
         <v>76.90000000000001</v>
       </c>
-      <c r="BG79" t="n">
+      <c r="BK79" t="n">
         <v>112.8</v>
       </c>
-      <c r="BH79" t="n">
-        <v>574</v>
-      </c>
-      <c r="BI79" t="n">
-        <v>381</v>
-      </c>
-      <c r="BJ79" t="n">
+      <c r="BL79" t="n">
         <v>165.6</v>
       </c>
     </row>
@@ -15515,24 +15993,30 @@
         <v>-104.1306311</v>
       </c>
       <c r="BD80" t="n">
+        <v>282</v>
+      </c>
+      <c r="BE80" t="n">
+        <v>190</v>
+      </c>
+      <c r="BF80" t="n">
+        <v>148</v>
+      </c>
+      <c r="BG80" t="n">
+        <v>134</v>
+      </c>
+      <c r="BH80" t="n">
         <v>71.2</v>
       </c>
-      <c r="BE80" t="n">
+      <c r="BI80" t="n">
         <v>120.3</v>
       </c>
-      <c r="BF80" t="n">
+      <c r="BJ80" t="n">
         <v>34.6</v>
       </c>
-      <c r="BG80" t="n">
+      <c r="BK80" t="n">
         <v>81.09999999999999</v>
       </c>
-      <c r="BH80" t="n">
-        <v>282</v>
-      </c>
-      <c r="BI80" t="n">
-        <v>190</v>
-      </c>
-      <c r="BJ80" t="n">
+      <c r="BL80" t="n">
         <v>153.2</v>
       </c>
     </row>
@@ -15703,24 +16187,30 @@
         <v>-102.6865238</v>
       </c>
       <c r="BD81" t="n">
+        <v>356</v>
+      </c>
+      <c r="BE81" t="n">
+        <v>239</v>
+      </c>
+      <c r="BF81" t="n">
+        <v>201</v>
+      </c>
+      <c r="BG81" t="n">
+        <v>155</v>
+      </c>
+      <c r="BH81" t="n">
         <v>72.8</v>
       </c>
-      <c r="BE81" t="n">
+      <c r="BI81" t="n">
         <v>120.6</v>
       </c>
-      <c r="BF81" t="n">
+      <c r="BJ81" t="n">
         <v>76.09999999999999</v>
       </c>
-      <c r="BG81" t="n">
+      <c r="BK81" t="n">
         <v>118.9</v>
       </c>
-      <c r="BH81" t="n">
-        <v>356</v>
-      </c>
-      <c r="BI81" t="n">
-        <v>239</v>
-      </c>
-      <c r="BJ81" t="n">
+      <c r="BL81" t="n">
         <v>154.1</v>
       </c>
     </row>
@@ -15891,24 +16381,30 @@
         <v>-102.8827986</v>
       </c>
       <c r="BD82" t="n">
+        <v>688</v>
+      </c>
+      <c r="BE82" t="n">
+        <v>444</v>
+      </c>
+      <c r="BF82" t="n">
+        <v>377</v>
+      </c>
+      <c r="BG82" t="n">
+        <v>310</v>
+      </c>
+      <c r="BH82" t="n">
         <v>68.3</v>
       </c>
-      <c r="BE82" t="n">
+      <c r="BI82" t="n">
         <v>132.8</v>
       </c>
-      <c r="BF82" t="n">
+      <c r="BJ82" t="n">
         <v>99.3</v>
       </c>
-      <c r="BG82" t="n">
+      <c r="BK82" t="n">
         <v>152.9</v>
       </c>
-      <c r="BH82" t="n">
-        <v>688</v>
-      </c>
-      <c r="BI82" t="n">
-        <v>444</v>
-      </c>
-      <c r="BJ82" t="n">
+      <c r="BL82" t="n">
         <v>131.7</v>
       </c>
     </row>
@@ -16079,24 +16575,30 @@
         <v>-102.50327</v>
       </c>
       <c r="BD83" t="n">
+        <v>1180</v>
+      </c>
+      <c r="BE83" t="n">
+        <v>730</v>
+      </c>
+      <c r="BF83" t="n">
+        <v>771</v>
+      </c>
+      <c r="BG83" t="n">
+        <v>409</v>
+      </c>
+      <c r="BH83" t="n">
         <v>117.4</v>
       </c>
-      <c r="BE83" t="n">
+      <c r="BI83" t="n">
         <v>163.2</v>
       </c>
-      <c r="BF83" t="n">
+      <c r="BJ83" t="n">
         <v>85.5</v>
       </c>
-      <c r="BG83" t="n">
+      <c r="BK83" t="n">
         <v>124.5</v>
       </c>
-      <c r="BH83" t="n">
-        <v>1180</v>
-      </c>
-      <c r="BI83" t="n">
-        <v>730</v>
-      </c>
-      <c r="BJ83" t="n">
+      <c r="BL83" t="n">
         <v>171.6</v>
       </c>
     </row>
@@ -16267,24 +16769,30 @@
         <v>-102.5106961</v>
       </c>
       <c r="BD84" t="n">
+        <v>321</v>
+      </c>
+      <c r="BE84" t="n">
+        <v>206</v>
+      </c>
+      <c r="BF84" t="n">
+        <v>156</v>
+      </c>
+      <c r="BG84" t="n">
+        <v>165</v>
+      </c>
+      <c r="BH84" t="n">
         <v>64.8</v>
       </c>
-      <c r="BE84" t="n">
+      <c r="BI84" t="n">
         <v>100.6</v>
       </c>
-      <c r="BF84" t="n">
+      <c r="BJ84" t="n">
         <v>48.1</v>
       </c>
-      <c r="BG84" t="n">
+      <c r="BK84" t="n">
         <v>89</v>
       </c>
-      <c r="BH84" t="n">
-        <v>321</v>
-      </c>
-      <c r="BI84" t="n">
-        <v>206</v>
-      </c>
-      <c r="BJ84" t="n">
+      <c r="BL84" t="n">
         <v>104</v>
       </c>
     </row>
@@ -16455,24 +16963,30 @@
         <v>-103.9118239</v>
       </c>
       <c r="BD85" t="n">
+        <v>500</v>
+      </c>
+      <c r="BE85" t="n">
+        <v>331</v>
+      </c>
+      <c r="BF85" t="n">
+        <v>228</v>
+      </c>
+      <c r="BG85" t="n">
+        <v>272</v>
+      </c>
+      <c r="BH85" t="n">
         <v>49.6</v>
       </c>
-      <c r="BE85" t="n">
+      <c r="BI85" t="n">
         <v>101.3</v>
       </c>
-      <c r="BF85" t="n">
+      <c r="BJ85" t="n">
         <v>58.7</v>
       </c>
-      <c r="BG85" t="n">
+      <c r="BK85" t="n">
         <v>110.6</v>
       </c>
-      <c r="BH85" t="n">
-        <v>500</v>
-      </c>
-      <c r="BI85" t="n">
-        <v>331</v>
-      </c>
-      <c r="BJ85" t="n">
+      <c r="BL85" t="n">
         <v>190.6</v>
       </c>
     </row>
@@ -16643,24 +17157,30 @@
         <v>-102.5148145</v>
       </c>
       <c r="BD86" t="n">
+        <v>205</v>
+      </c>
+      <c r="BE86" t="n">
+        <v>121</v>
+      </c>
+      <c r="BF86" t="n">
+        <v>101</v>
+      </c>
+      <c r="BG86" t="n">
+        <v>104</v>
+      </c>
+      <c r="BH86" t="n">
         <v>41.7</v>
       </c>
-      <c r="BE86" t="n">
+      <c r="BI86" t="n">
         <v>72.40000000000001</v>
       </c>
-      <c r="BF86" t="n">
+      <c r="BJ86" t="n">
         <v>16.5</v>
       </c>
-      <c r="BG86" t="n">
+      <c r="BK86" t="n">
         <v>46.3</v>
       </c>
-      <c r="BH86" t="n">
-        <v>205</v>
-      </c>
-      <c r="BI86" t="n">
-        <v>121</v>
-      </c>
-      <c r="BJ86" t="n">
+      <c r="BL86" t="n">
         <v>108</v>
       </c>
     </row>
@@ -16831,24 +17351,30 @@
         <v>-102.9513719</v>
       </c>
       <c r="BD87" t="n">
+        <v>327</v>
+      </c>
+      <c r="BE87" t="n">
+        <v>197</v>
+      </c>
+      <c r="BF87" t="n">
+        <v>84</v>
+      </c>
+      <c r="BG87" t="n">
+        <v>243</v>
+      </c>
+      <c r="BH87" t="n">
         <v>40</v>
       </c>
-      <c r="BE87" t="n">
+      <c r="BI87" t="n">
         <v>126</v>
       </c>
-      <c r="BF87" t="n">
+      <c r="BJ87" t="n">
         <v>31.7</v>
       </c>
-      <c r="BG87" t="n">
+      <c r="BK87" t="n">
         <v>59.2</v>
       </c>
-      <c r="BH87" t="n">
-        <v>327</v>
-      </c>
-      <c r="BI87" t="n">
-        <v>197</v>
-      </c>
-      <c r="BJ87" t="n">
+      <c r="BL87" t="n">
         <v>146.3</v>
       </c>
     </row>
@@ -17019,24 +17545,30 @@
         <v>-103.8327867</v>
       </c>
       <c r="BD88" t="n">
+        <v>215</v>
+      </c>
+      <c r="BE88" t="n">
+        <v>142</v>
+      </c>
+      <c r="BF88" t="n">
+        <v>83</v>
+      </c>
+      <c r="BG88" t="n">
+        <v>132</v>
+      </c>
+      <c r="BH88" t="n">
         <v>87.7</v>
       </c>
-      <c r="BE88" t="n">
+      <c r="BI88" t="n">
         <v>131.2</v>
       </c>
-      <c r="BF88" t="n">
+      <c r="BJ88" t="n">
         <v>38.6</v>
       </c>
-      <c r="BG88" t="n">
+      <c r="BK88" t="n">
         <v>159.6</v>
       </c>
-      <c r="BH88" t="n">
-        <v>215</v>
-      </c>
-      <c r="BI88" t="n">
-        <v>142</v>
-      </c>
-      <c r="BJ88" t="n">
+      <c r="BL88" t="n">
         <v>243.2</v>
       </c>
     </row>
@@ -17207,24 +17739,30 @@
         <v>-103.0314246</v>
       </c>
       <c r="BD89" t="n">
+        <v>251</v>
+      </c>
+      <c r="BE89" t="n">
+        <v>171</v>
+      </c>
+      <c r="BF89" t="n">
+        <v>98</v>
+      </c>
+      <c r="BG89" t="n">
+        <v>153</v>
+      </c>
+      <c r="BH89" t="n">
         <v>37.5</v>
       </c>
-      <c r="BE89" t="n">
+      <c r="BI89" t="n">
         <v>94.2</v>
       </c>
-      <c r="BF89" t="n">
+      <c r="BJ89" t="n">
         <v>61.6</v>
       </c>
-      <c r="BG89" t="n">
+      <c r="BK89" t="n">
         <v>127.8</v>
       </c>
-      <c r="BH89" t="n">
-        <v>251</v>
-      </c>
-      <c r="BI89" t="n">
-        <v>171</v>
-      </c>
-      <c r="BJ89" t="n">
+      <c r="BL89" t="n">
         <v>157.8</v>
       </c>
     </row>
@@ -17395,24 +17933,30 @@
         <v>-103.6855272</v>
       </c>
       <c r="BD90" t="n">
+        <v>329</v>
+      </c>
+      <c r="BE90" t="n">
+        <v>205</v>
+      </c>
+      <c r="BF90" t="n">
+        <v>146</v>
+      </c>
+      <c r="BG90" t="n">
+        <v>183</v>
+      </c>
+      <c r="BH90" t="n">
         <v>43.1</v>
       </c>
-      <c r="BE90" t="n">
+      <c r="BI90" t="n">
         <v>140.3</v>
       </c>
-      <c r="BF90" t="n">
+      <c r="BJ90" t="n">
         <v>105</v>
       </c>
-      <c r="BG90" t="n">
+      <c r="BK90" t="n">
         <v>164.3</v>
       </c>
-      <c r="BH90" t="n">
-        <v>329</v>
-      </c>
-      <c r="BI90" t="n">
-        <v>205</v>
-      </c>
-      <c r="BJ90" t="n">
+      <c r="BL90" t="n">
         <v>174.2</v>
       </c>
     </row>
@@ -17583,24 +18127,30 @@
         <v>-102.2813711</v>
       </c>
       <c r="BD91" t="n">
+        <v>669</v>
+      </c>
+      <c r="BE91" t="n">
+        <v>427</v>
+      </c>
+      <c r="BF91" t="n">
+        <v>308</v>
+      </c>
+      <c r="BG91" t="n">
+        <v>361</v>
+      </c>
+      <c r="BH91" t="n">
         <v>66.5</v>
       </c>
-      <c r="BE91" t="n">
+      <c r="BI91" t="n">
         <v>113.4</v>
       </c>
-      <c r="BF91" t="n">
+      <c r="BJ91" t="n">
         <v>58.1</v>
       </c>
-      <c r="BG91" t="n">
+      <c r="BK91" t="n">
         <v>100.6</v>
       </c>
-      <c r="BH91" t="n">
-        <v>669</v>
-      </c>
-      <c r="BI91" t="n">
-        <v>427</v>
-      </c>
-      <c r="BJ91" t="n">
+      <c r="BL91" t="n">
         <v>94.09999999999999</v>
       </c>
     </row>
@@ -17771,24 +18321,30 @@
         <v>-103.2498781</v>
       </c>
       <c r="BD92" t="n">
+        <v>272</v>
+      </c>
+      <c r="BE92" t="n">
+        <v>186</v>
+      </c>
+      <c r="BF92" t="n">
+        <v>120</v>
+      </c>
+      <c r="BG92" t="n">
+        <v>152</v>
+      </c>
+      <c r="BH92" t="n">
         <v>53.2</v>
       </c>
-      <c r="BE92" t="n">
+      <c r="BI92" t="n">
         <v>102.7</v>
       </c>
-      <c r="BF92" t="n">
+      <c r="BJ92" t="n">
         <v>52.9</v>
       </c>
-      <c r="BG92" t="n">
+      <c r="BK92" t="n">
         <v>96.09999999999999</v>
       </c>
-      <c r="BH92" t="n">
-        <v>272</v>
-      </c>
-      <c r="BI92" t="n">
-        <v>186</v>
-      </c>
-      <c r="BJ92" t="n">
+      <c r="BL92" t="n">
         <v>141.7</v>
       </c>
     </row>
@@ -17959,24 +18515,30 @@
         <v>-103.6013032</v>
       </c>
       <c r="BD93" t="n">
+        <v>311</v>
+      </c>
+      <c r="BE93" t="n">
+        <v>206</v>
+      </c>
+      <c r="BF93" t="n">
+        <v>164</v>
+      </c>
+      <c r="BG93" t="n">
+        <v>146</v>
+      </c>
+      <c r="BH93" t="n">
         <v>50.9</v>
       </c>
-      <c r="BE93" t="n">
+      <c r="BI93" t="n">
         <v>114.6</v>
       </c>
-      <c r="BF93" t="n">
+      <c r="BJ93" t="n">
         <v>61.5</v>
       </c>
-      <c r="BG93" t="n">
+      <c r="BK93" t="n">
         <v>122.6</v>
       </c>
-      <c r="BH93" t="n">
-        <v>311</v>
-      </c>
-      <c r="BI93" t="n">
-        <v>206</v>
-      </c>
-      <c r="BJ93" t="n">
+      <c r="BL93" t="n">
         <v>121.4</v>
       </c>
     </row>
@@ -18147,24 +18709,30 @@
         <v>-102.7494169</v>
       </c>
       <c r="BD94" t="n">
+        <v>343</v>
+      </c>
+      <c r="BE94" t="n">
+        <v>213</v>
+      </c>
+      <c r="BF94" t="n">
+        <v>188</v>
+      </c>
+      <c r="BG94" t="n">
+        <v>155</v>
+      </c>
+      <c r="BH94" t="n">
         <v>110.7</v>
       </c>
-      <c r="BE94" t="n">
+      <c r="BI94" t="n">
         <v>163.3</v>
       </c>
-      <c r="BF94" t="n">
+      <c r="BJ94" t="n">
         <v>55.3</v>
       </c>
-      <c r="BG94" t="n">
+      <c r="BK94" t="n">
         <v>95.7</v>
       </c>
-      <c r="BH94" t="n">
-        <v>343</v>
-      </c>
-      <c r="BI94" t="n">
-        <v>213</v>
-      </c>
-      <c r="BJ94" t="n">
+      <c r="BL94" t="n">
         <v>145.6</v>
       </c>
     </row>
@@ -18335,24 +18903,30 @@
         <v>-102.9230291</v>
       </c>
       <c r="BD95" t="n">
+        <v>210</v>
+      </c>
+      <c r="BE95" t="n">
+        <v>123</v>
+      </c>
+      <c r="BF95" t="n">
+        <v>126</v>
+      </c>
+      <c r="BG95" t="n">
+        <v>83</v>
+      </c>
+      <c r="BH95" t="n">
         <v>97.59999999999999</v>
       </c>
-      <c r="BE95" t="n">
+      <c r="BI95" t="n">
         <v>142.6</v>
       </c>
-      <c r="BF95" t="n">
+      <c r="BJ95" t="n">
         <v>27.9</v>
       </c>
-      <c r="BG95" t="n">
+      <c r="BK95" t="n">
         <v>45.9</v>
       </c>
-      <c r="BH95" t="n">
-        <v>210</v>
-      </c>
-      <c r="BI95" t="n">
-        <v>123</v>
-      </c>
-      <c r="BJ95" t="n">
+      <c r="BL95" t="n">
         <v>99.2</v>
       </c>
     </row>
@@ -18521,24 +19095,30 @@
         <v>-104.1102848</v>
       </c>
       <c r="BD96" t="n">
+        <v>86</v>
+      </c>
+      <c r="BE96" t="n">
+        <v>54</v>
+      </c>
+      <c r="BF96" t="n">
+        <v>45</v>
+      </c>
+      <c r="BG96" t="n">
+        <v>41</v>
+      </c>
+      <c r="BH96" t="n">
         <v>31.9</v>
       </c>
-      <c r="BE96" t="n">
+      <c r="BI96" t="n">
         <v>43.7</v>
       </c>
-      <c r="BF96" t="n">
+      <c r="BJ96" t="n">
         <v>31.7</v>
       </c>
-      <c r="BG96" t="n">
+      <c r="BK96" t="n">
         <v>68.90000000000001</v>
       </c>
-      <c r="BH96" t="n">
-        <v>86</v>
-      </c>
-      <c r="BI96" t="n">
-        <v>54</v>
-      </c>
-      <c r="BJ96" t="n">
+      <c r="BL96" t="n">
         <v>37.9</v>
       </c>
     </row>
@@ -18709,24 +19289,30 @@
         <v>-103.4114705</v>
       </c>
       <c r="BD97" t="n">
+        <v>507</v>
+      </c>
+      <c r="BE97" t="n">
+        <v>318</v>
+      </c>
+      <c r="BF97" t="n">
+        <v>289</v>
+      </c>
+      <c r="BG97" t="n">
+        <v>218</v>
+      </c>
+      <c r="BH97" t="n">
         <v>74.8</v>
       </c>
-      <c r="BE97" t="n">
+      <c r="BI97" t="n">
         <v>125.1</v>
       </c>
-      <c r="BF97" t="n">
+      <c r="BJ97" t="n">
         <v>87.59999999999999</v>
       </c>
-      <c r="BG97" t="n">
+      <c r="BK97" t="n">
         <v>115.5</v>
       </c>
-      <c r="BH97" t="n">
-        <v>507</v>
-      </c>
-      <c r="BI97" t="n">
-        <v>318</v>
-      </c>
-      <c r="BJ97" t="n">
+      <c r="BL97" t="n">
         <v>130.8</v>
       </c>
     </row>
@@ -18897,24 +19483,30 @@
         <v>-103.817421</v>
       </c>
       <c r="BD98" t="n">
+        <v>523</v>
+      </c>
+      <c r="BE98" t="n">
+        <v>327</v>
+      </c>
+      <c r="BF98" t="n">
+        <v>240</v>
+      </c>
+      <c r="BG98" t="n">
+        <v>281</v>
+      </c>
+      <c r="BH98" t="n">
         <v>35.9</v>
       </c>
-      <c r="BE98" t="n">
+      <c r="BI98" t="n">
         <v>84</v>
       </c>
-      <c r="BF98" t="n">
+      <c r="BJ98" t="n">
         <v>62.3</v>
       </c>
-      <c r="BG98" t="n">
+      <c r="BK98" t="n">
         <v>121.2</v>
       </c>
-      <c r="BH98" t="n">
-        <v>523</v>
-      </c>
-      <c r="BI98" t="n">
-        <v>327</v>
-      </c>
-      <c r="BJ98" t="n">
+      <c r="BL98" t="n">
         <v>171.1</v>
       </c>
     </row>
@@ -19085,24 +19677,30 @@
         <v>-103.0515186</v>
       </c>
       <c r="BD99" t="n">
+        <v>937</v>
+      </c>
+      <c r="BE99" t="n">
+        <v>598</v>
+      </c>
+      <c r="BF99" t="n">
+        <v>554</v>
+      </c>
+      <c r="BG99" t="n">
+        <v>383</v>
+      </c>
+      <c r="BH99" t="n">
         <v>77.3</v>
       </c>
-      <c r="BE99" t="n">
+      <c r="BI99" t="n">
         <v>133.9</v>
       </c>
-      <c r="BF99" t="n">
+      <c r="BJ99" t="n">
         <v>56.9</v>
       </c>
-      <c r="BG99" t="n">
+      <c r="BK99" t="n">
         <v>108.5</v>
       </c>
-      <c r="BH99" t="n">
-        <v>937</v>
-      </c>
-      <c r="BI99" t="n">
-        <v>598</v>
-      </c>
-      <c r="BJ99" t="n">
+      <c r="BL99" t="n">
         <v>152.5</v>
       </c>
     </row>
@@ -19273,24 +19871,30 @@
         <v>-103.7075033</v>
       </c>
       <c r="BD100" t="n">
+        <v>1130</v>
+      </c>
+      <c r="BE100" t="n">
+        <v>749</v>
+      </c>
+      <c r="BF100" t="n">
+        <v>571</v>
+      </c>
+      <c r="BG100" t="n">
+        <v>559</v>
+      </c>
+      <c r="BH100" t="n">
         <v>77.2</v>
       </c>
-      <c r="BE100" t="n">
+      <c r="BI100" t="n">
         <v>163.4</v>
       </c>
-      <c r="BF100" t="n">
+      <c r="BJ100" t="n">
         <v>73.09999999999999</v>
       </c>
-      <c r="BG100" t="n">
+      <c r="BK100" t="n">
         <v>132.6</v>
       </c>
-      <c r="BH100" t="n">
-        <v>1130</v>
-      </c>
-      <c r="BI100" t="n">
-        <v>749</v>
-      </c>
-      <c r="BJ100" t="n">
+      <c r="BL100" t="n">
         <v>131.3</v>
       </c>
     </row>
@@ -19461,24 +20065,30 @@
         <v>-103.7048985</v>
       </c>
       <c r="BD101" t="n">
+        <v>288</v>
+      </c>
+      <c r="BE101" t="n">
+        <v>187</v>
+      </c>
+      <c r="BF101" t="n">
+        <v>168</v>
+      </c>
+      <c r="BG101" t="n">
+        <v>120</v>
+      </c>
+      <c r="BH101" t="n">
         <v>105.4</v>
       </c>
-      <c r="BE101" t="n">
+      <c r="BI101" t="n">
         <v>183</v>
       </c>
-      <c r="BF101" t="n">
+      <c r="BJ101" t="n">
         <v>84.8</v>
       </c>
-      <c r="BG101" t="n">
+      <c r="BK101" t="n">
         <v>126.2</v>
       </c>
-      <c r="BH101" t="n">
-        <v>288</v>
-      </c>
-      <c r="BI101" t="n">
-        <v>187</v>
-      </c>
-      <c r="BJ101" t="n">
+      <c r="BL101" t="n">
         <v>139.8</v>
       </c>
     </row>
@@ -19649,24 +20259,30 @@
         <v>-103.2050488</v>
       </c>
       <c r="BD102" t="n">
+        <v>591</v>
+      </c>
+      <c r="BE102" t="n">
+        <v>389</v>
+      </c>
+      <c r="BF102" t="n">
+        <v>303</v>
+      </c>
+      <c r="BG102" t="n">
+        <v>288</v>
+      </c>
+      <c r="BH102" t="n">
         <v>71</v>
       </c>
-      <c r="BE102" t="n">
+      <c r="BI102" t="n">
         <v>101.5</v>
       </c>
-      <c r="BF102" t="n">
+      <c r="BJ102" t="n">
         <v>62.1</v>
       </c>
-      <c r="BG102" t="n">
+      <c r="BK102" t="n">
         <v>134.6</v>
       </c>
-      <c r="BH102" t="n">
-        <v>591</v>
-      </c>
-      <c r="BI102" t="n">
-        <v>389</v>
-      </c>
-      <c r="BJ102" t="n">
+      <c r="BL102" t="n">
         <v>81</v>
       </c>
     </row>
@@ -19837,24 +20453,30 @@
         <v>-104.1778165</v>
       </c>
       <c r="BD103" t="n">
+        <v>438</v>
+      </c>
+      <c r="BE103" t="n">
+        <v>272</v>
+      </c>
+      <c r="BF103" t="n">
+        <v>157</v>
+      </c>
+      <c r="BG103" t="n">
+        <v>281</v>
+      </c>
+      <c r="BH103" t="n">
         <v>63.9</v>
       </c>
-      <c r="BE103" t="n">
+      <c r="BI103" t="n">
         <v>147.9</v>
       </c>
-      <c r="BF103" t="n">
+      <c r="BJ103" t="n">
         <v>20.9</v>
       </c>
-      <c r="BG103" t="n">
+      <c r="BK103" t="n">
         <v>94.5</v>
       </c>
-      <c r="BH103" t="n">
-        <v>438</v>
-      </c>
-      <c r="BI103" t="n">
-        <v>272</v>
-      </c>
-      <c r="BJ103" t="n">
+      <c r="BL103" t="n">
         <v>169.4</v>
       </c>
     </row>
@@ -20025,24 +20647,30 @@
         <v>-102.758809</v>
       </c>
       <c r="BD104" t="n">
+        <v>1418</v>
+      </c>
+      <c r="BE104" t="n">
+        <v>909</v>
+      </c>
+      <c r="BF104" t="n">
+        <v>667</v>
+      </c>
+      <c r="BG104" t="n">
+        <v>751</v>
+      </c>
+      <c r="BH104" t="n">
         <v>40.9</v>
       </c>
-      <c r="BE104" t="n">
+      <c r="BI104" t="n">
         <v>105</v>
       </c>
-      <c r="BF104" t="n">
+      <c r="BJ104" t="n">
         <v>52.9</v>
       </c>
-      <c r="BG104" t="n">
+      <c r="BK104" t="n">
         <v>88.59999999999999</v>
       </c>
-      <c r="BH104" t="n">
-        <v>1418</v>
-      </c>
-      <c r="BI104" t="n">
-        <v>909</v>
-      </c>
-      <c r="BJ104" t="n">
+      <c r="BL104" t="n">
         <v>96.5</v>
       </c>
     </row>
@@ -20213,24 +20841,30 @@
         <v>-102.3142822</v>
       </c>
       <c r="BD105" t="n">
+        <v>809</v>
+      </c>
+      <c r="BE105" t="n">
+        <v>532</v>
+      </c>
+      <c r="BF105" t="n">
+        <v>433</v>
+      </c>
+      <c r="BG105" t="n">
+        <v>376</v>
+      </c>
+      <c r="BH105" t="n">
         <v>58.8</v>
       </c>
-      <c r="BE105" t="n">
+      <c r="BI105" t="n">
         <v>117.1</v>
       </c>
-      <c r="BF105" t="n">
+      <c r="BJ105" t="n">
         <v>42.7</v>
       </c>
-      <c r="BG105" t="n">
+      <c r="BK105" t="n">
         <v>90.59999999999999</v>
       </c>
-      <c r="BH105" t="n">
-        <v>809</v>
-      </c>
-      <c r="BI105" t="n">
-        <v>532</v>
-      </c>
-      <c r="BJ105" t="n">
+      <c r="BL105" t="n">
         <v>104</v>
       </c>
     </row>
@@ -20401,24 +21035,30 @@
         <v>-102.768809</v>
       </c>
       <c r="BD106" t="n">
+        <v>1540</v>
+      </c>
+      <c r="BE106" t="n">
+        <v>931</v>
+      </c>
+      <c r="BF106" t="n">
+        <v>786</v>
+      </c>
+      <c r="BG106" t="n">
+        <v>754</v>
+      </c>
+      <c r="BH106" t="n">
         <v>72.8</v>
       </c>
-      <c r="BE106" t="n">
+      <c r="BI106" t="n">
         <v>157.3</v>
       </c>
-      <c r="BF106" t="n">
+      <c r="BJ106" t="n">
         <v>64.5</v>
       </c>
-      <c r="BG106" t="n">
+      <c r="BK106" t="n">
         <v>120.6</v>
       </c>
-      <c r="BH106" t="n">
-        <v>1540</v>
-      </c>
-      <c r="BI106" t="n">
-        <v>931</v>
-      </c>
-      <c r="BJ106" t="n">
+      <c r="BL106" t="n">
         <v>140.9</v>
       </c>
     </row>
@@ -20589,24 +21229,30 @@
         <v>-102.9101603</v>
       </c>
       <c r="BD107" t="n">
+        <v>199</v>
+      </c>
+      <c r="BE107" t="n">
+        <v>124</v>
+      </c>
+      <c r="BF107" t="n">
+        <v>73</v>
+      </c>
+      <c r="BG107" t="n">
+        <v>126</v>
+      </c>
+      <c r="BH107" t="n">
         <v>17.2</v>
       </c>
-      <c r="BE107" t="n">
+      <c r="BI107" t="n">
         <v>85.5</v>
       </c>
-      <c r="BF107" t="n">
+      <c r="BJ107" t="n">
         <v>19.1</v>
       </c>
-      <c r="BG107" t="n">
+      <c r="BK107" t="n">
         <v>53.4</v>
       </c>
-      <c r="BH107" t="n">
-        <v>199</v>
-      </c>
-      <c r="BI107" t="n">
-        <v>124</v>
-      </c>
-      <c r="BJ107" t="n">
+      <c r="BL107" t="n">
         <v>83.2</v>
       </c>
     </row>
@@ -20777,24 +21423,30 @@
         <v>-102.4045943</v>
       </c>
       <c r="BD108" t="n">
+        <v>337</v>
+      </c>
+      <c r="BE108" t="n">
+        <v>231</v>
+      </c>
+      <c r="BF108" t="n">
+        <v>189</v>
+      </c>
+      <c r="BG108" t="n">
+        <v>148</v>
+      </c>
+      <c r="BH108" t="n">
         <v>67.90000000000001</v>
       </c>
-      <c r="BE108" t="n">
+      <c r="BI108" t="n">
         <v>108.9</v>
       </c>
-      <c r="BF108" t="n">
+      <c r="BJ108" t="n">
         <v>64.3</v>
       </c>
-      <c r="BG108" t="n">
+      <c r="BK108" t="n">
         <v>100.1</v>
       </c>
-      <c r="BH108" t="n">
-        <v>337</v>
-      </c>
-      <c r="BI108" t="n">
-        <v>231</v>
-      </c>
-      <c r="BJ108" t="n">
+      <c r="BL108" t="n">
         <v>119</v>
       </c>
     </row>
@@ -20965,24 +21617,30 @@
         <v>-103.9753944</v>
       </c>
       <c r="BD109" t="n">
+        <v>359</v>
+      </c>
+      <c r="BE109" t="n">
+        <v>217</v>
+      </c>
+      <c r="BF109" t="n">
+        <v>206</v>
+      </c>
+      <c r="BG109" t="n">
+        <v>153</v>
+      </c>
+      <c r="BH109" t="n">
         <v>100.1</v>
       </c>
-      <c r="BE109" t="n">
+      <c r="BI109" t="n">
         <v>169.5</v>
       </c>
-      <c r="BF109" t="n">
+      <c r="BJ109" t="n">
         <v>76.09999999999999</v>
       </c>
-      <c r="BG109" t="n">
+      <c r="BK109" t="n">
         <v>126.5</v>
       </c>
-      <c r="BH109" t="n">
-        <v>359</v>
-      </c>
-      <c r="BI109" t="n">
-        <v>217</v>
-      </c>
-      <c r="BJ109" t="n">
+      <c r="BL109" t="n">
         <v>147.4</v>
       </c>
     </row>
@@ -21153,24 +21811,30 @@
         <v>-102.5175664</v>
       </c>
       <c r="BD110" t="n">
+        <v>714</v>
+      </c>
+      <c r="BE110" t="n">
+        <v>474</v>
+      </c>
+      <c r="BF110" t="n">
+        <v>439</v>
+      </c>
+      <c r="BG110" t="n">
+        <v>275</v>
+      </c>
+      <c r="BH110" t="n">
         <v>67.7</v>
       </c>
-      <c r="BE110" t="n">
+      <c r="BI110" t="n">
         <v>102.2</v>
       </c>
-      <c r="BF110" t="n">
+      <c r="BJ110" t="n">
         <v>69.90000000000001</v>
       </c>
-      <c r="BG110" t="n">
+      <c r="BK110" t="n">
         <v>120.1</v>
       </c>
-      <c r="BH110" t="n">
-        <v>714</v>
-      </c>
-      <c r="BI110" t="n">
-        <v>474</v>
-      </c>
-      <c r="BJ110" t="n">
+      <c r="BL110" t="n">
         <v>117.8</v>
       </c>
     </row>
@@ -21341,24 +22005,30 @@
         <v>-103.2743171</v>
       </c>
       <c r="BD111" t="n">
+        <v>249</v>
+      </c>
+      <c r="BE111" t="n">
+        <v>155</v>
+      </c>
+      <c r="BF111" t="n">
+        <v>113</v>
+      </c>
+      <c r="BG111" t="n">
+        <v>136</v>
+      </c>
+      <c r="BH111" t="n">
         <v>74.2</v>
       </c>
-      <c r="BE111" t="n">
+      <c r="BI111" t="n">
         <v>109.2</v>
       </c>
-      <c r="BF111" t="n">
+      <c r="BJ111" t="n">
         <v>31.7</v>
       </c>
-      <c r="BG111" t="n">
+      <c r="BK111" t="n">
         <v>65.3</v>
       </c>
-      <c r="BH111" t="n">
-        <v>249</v>
-      </c>
-      <c r="BI111" t="n">
-        <v>155</v>
-      </c>
-      <c r="BJ111" t="n">
+      <c r="BL111" t="n">
         <v>120</v>
       </c>
     </row>
@@ -21529,24 +22199,30 @@
         <v>-103.4368646</v>
       </c>
       <c r="BD112" t="n">
+        <v>630</v>
+      </c>
+      <c r="BE112" t="n">
+        <v>411</v>
+      </c>
+      <c r="BF112" t="n">
+        <v>361</v>
+      </c>
+      <c r="BG112" t="n">
+        <v>269</v>
+      </c>
+      <c r="BH112" t="n">
         <v>76.09999999999999</v>
       </c>
-      <c r="BE112" t="n">
+      <c r="BI112" t="n">
         <v>123.1</v>
       </c>
-      <c r="BF112" t="n">
+      <c r="BJ112" t="n">
         <v>80.09999999999999</v>
       </c>
-      <c r="BG112" t="n">
+      <c r="BK112" t="n">
         <v>117</v>
       </c>
-      <c r="BH112" t="n">
-        <v>630</v>
-      </c>
-      <c r="BI112" t="n">
-        <v>411</v>
-      </c>
-      <c r="BJ112" t="n">
+      <c r="BL112" t="n">
         <v>137.4</v>
       </c>
     </row>
@@ -21717,24 +22393,30 @@
         <v>-103.4005097</v>
       </c>
       <c r="BD113" t="n">
+        <v>4452</v>
+      </c>
+      <c r="BE113" t="n">
+        <v>3018</v>
+      </c>
+      <c r="BF113" t="n">
+        <v>2267</v>
+      </c>
+      <c r="BG113" t="n">
+        <v>2181</v>
+      </c>
+      <c r="BH113" t="n">
         <v>57.6</v>
       </c>
-      <c r="BE113" t="n">
+      <c r="BI113" t="n">
         <v>122.2</v>
       </c>
-      <c r="BF113" t="n">
+      <c r="BJ113" t="n">
         <v>71.40000000000001</v>
       </c>
-      <c r="BG113" t="n">
+      <c r="BK113" t="n">
         <v>120.6</v>
       </c>
-      <c r="BH113" t="n">
-        <v>4452</v>
-      </c>
-      <c r="BI113" t="n">
-        <v>3018</v>
-      </c>
-      <c r="BJ113" t="n">
+      <c r="BL113" t="n">
         <v>61.9</v>
       </c>
     </row>
@@ -21905,24 +22587,30 @@
         <v>-103.1507254</v>
       </c>
       <c r="BD114" t="n">
+        <v>240</v>
+      </c>
+      <c r="BE114" t="n">
+        <v>160</v>
+      </c>
+      <c r="BF114" t="n">
+        <v>135</v>
+      </c>
+      <c r="BG114" t="n">
+        <v>105</v>
+      </c>
+      <c r="BH114" t="n">
         <v>74.8</v>
       </c>
-      <c r="BE114" t="n">
+      <c r="BI114" t="n">
         <v>132.5</v>
       </c>
-      <c r="BF114" t="n">
+      <c r="BJ114" t="n">
         <v>47.8</v>
       </c>
-      <c r="BG114" t="n">
+      <c r="BK114" t="n">
         <v>99.40000000000001</v>
       </c>
-      <c r="BH114" t="n">
-        <v>240</v>
-      </c>
-      <c r="BI114" t="n">
-        <v>160</v>
-      </c>
-      <c r="BJ114" t="n">
+      <c r="BL114" t="n">
         <v>74.2</v>
       </c>
     </row>
@@ -22093,24 +22781,30 @@
         <v>-103.3120428</v>
       </c>
       <c r="BD115" t="n">
+        <v>7259</v>
+      </c>
+      <c r="BE115" t="n">
+        <v>4630</v>
+      </c>
+      <c r="BF115" t="n">
+        <v>3489</v>
+      </c>
+      <c r="BG115" t="n">
+        <v>3765</v>
+      </c>
+      <c r="BH115" t="n">
         <v>66.40000000000001</v>
       </c>
-      <c r="BE115" t="n">
+      <c r="BI115" t="n">
         <v>132.9</v>
       </c>
-      <c r="BF115" t="n">
+      <c r="BJ115" t="n">
         <v>54</v>
       </c>
-      <c r="BG115" t="n">
+      <c r="BK115" t="n">
         <v>99.3</v>
       </c>
-      <c r="BH115" t="n">
-        <v>7259</v>
-      </c>
-      <c r="BI115" t="n">
-        <v>4630</v>
-      </c>
-      <c r="BJ115" t="n">
+      <c r="BL115" t="n">
         <v>106.3</v>
       </c>
     </row>
@@ -22281,24 +22975,30 @@
         <v>-103.8101371</v>
       </c>
       <c r="BD116" t="n">
+        <v>522</v>
+      </c>
+      <c r="BE116" t="n">
+        <v>344</v>
+      </c>
+      <c r="BF116" t="n">
+        <v>262</v>
+      </c>
+      <c r="BG116" t="n">
+        <v>260</v>
+      </c>
+      <c r="BH116" t="n">
         <v>72.3</v>
       </c>
-      <c r="BE116" t="n">
+      <c r="BI116" t="n">
         <v>127.3</v>
       </c>
-      <c r="BF116" t="n">
+      <c r="BJ116" t="n">
         <v>78.3</v>
       </c>
-      <c r="BG116" t="n">
+      <c r="BK116" t="n">
         <v>136.4</v>
       </c>
-      <c r="BH116" t="n">
-        <v>522</v>
-      </c>
-      <c r="BI116" t="n">
-        <v>344</v>
-      </c>
-      <c r="BJ116" t="n">
+      <c r="BL116" t="n">
         <v>122.7</v>
       </c>
     </row>
@@ -22469,24 +23169,30 @@
         <v>-103.2421263</v>
       </c>
       <c r="BD117" t="n">
+        <v>5495</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>3530</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>2769</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>2723</v>
+      </c>
+      <c r="BH117" t="n">
         <v>82.09999999999999</v>
       </c>
-      <c r="BE117" t="n">
+      <c r="BI117" t="n">
         <v>145.7</v>
       </c>
-      <c r="BF117" t="n">
+      <c r="BJ117" t="n">
         <v>71.2</v>
       </c>
-      <c r="BG117" t="n">
+      <c r="BK117" t="n">
         <v>119.3</v>
       </c>
-      <c r="BH117" t="n">
-        <v>5495</v>
-      </c>
-      <c r="BI117" t="n">
-        <v>3530</v>
-      </c>
-      <c r="BJ117" t="n">
+      <c r="BL117" t="n">
         <v>97.40000000000001</v>
       </c>
     </row>
@@ -22657,24 +23363,30 @@
         <v>-103.3913671</v>
       </c>
       <c r="BD118" t="n">
+        <v>13254</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>8551</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>5986</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>7265</v>
+      </c>
+      <c r="BH118" t="n">
         <v>51.9</v>
       </c>
-      <c r="BE118" t="n">
+      <c r="BI118" t="n">
         <v>112.5</v>
       </c>
-      <c r="BF118" t="n">
+      <c r="BJ118" t="n">
         <v>37.6</v>
       </c>
-      <c r="BG118" t="n">
+      <c r="BK118" t="n">
         <v>72.09999999999999</v>
       </c>
-      <c r="BH118" t="n">
-        <v>13254</v>
-      </c>
-      <c r="BI118" t="n">
-        <v>8551</v>
-      </c>
-      <c r="BJ118" t="n">
+      <c r="BL118" t="n">
         <v>90.3</v>
       </c>
     </row>
@@ -22845,24 +23557,30 @@
         <v>-103.1813141</v>
       </c>
       <c r="BD119" t="n">
+        <v>2052</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>1305</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>1095</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>956</v>
+      </c>
+      <c r="BH119" t="n">
         <v>89.40000000000001</v>
       </c>
-      <c r="BE119" t="n">
+      <c r="BI119" t="n">
         <v>165.4</v>
       </c>
-      <c r="BF119" t="n">
+      <c r="BJ119" t="n">
         <v>73.2</v>
       </c>
-      <c r="BG119" t="n">
+      <c r="BK119" t="n">
         <v>115.2</v>
       </c>
-      <c r="BH119" t="n">
-        <v>2052</v>
-      </c>
-      <c r="BI119" t="n">
-        <v>1305</v>
-      </c>
-      <c r="BJ119" t="n">
+      <c r="BL119" t="n">
         <v>76.8</v>
       </c>
     </row>
@@ -23033,24 +23751,30 @@
         <v>-103.2203586</v>
       </c>
       <c r="BD120" t="n">
+        <v>681</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>439</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>395</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>286</v>
+      </c>
+      <c r="BH120" t="n">
         <v>63.1</v>
       </c>
-      <c r="BE120" t="n">
+      <c r="BI120" t="n">
         <v>104</v>
       </c>
-      <c r="BF120" t="n">
+      <c r="BJ120" t="n">
         <v>46.6</v>
       </c>
-      <c r="BG120" t="n">
+      <c r="BK120" t="n">
         <v>72</v>
       </c>
-      <c r="BH120" t="n">
-        <v>681</v>
-      </c>
-      <c r="BI120" t="n">
-        <v>439</v>
-      </c>
-      <c r="BJ120" t="n">
+      <c r="BL120" t="n">
         <v>122.6</v>
       </c>
     </row>
@@ -23219,24 +23943,30 @@
         <v>-103.7915405</v>
       </c>
       <c r="BD121" t="n">
+        <v>36</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>25</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>17</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>19</v>
+      </c>
+      <c r="BH121" t="n">
         <v>62</v>
       </c>
-      <c r="BE121" t="n">
+      <c r="BI121" t="n">
         <v>75.7</v>
       </c>
-      <c r="BF121" t="n">
+      <c r="BJ121" t="n">
         <v>11.4</v>
       </c>
-      <c r="BG121" t="n">
+      <c r="BK121" t="n">
         <v>81.90000000000001</v>
       </c>
-      <c r="BH121" t="n">
-        <v>36</v>
-      </c>
-      <c r="BI121" t="n">
-        <v>25</v>
-      </c>
-      <c r="BJ121" t="n">
+      <c r="BL121" t="n">
         <v>135</v>
       </c>
     </row>
@@ -23407,24 +24137,30 @@
         <v>-104.1398092</v>
       </c>
       <c r="BD122" t="n">
+        <v>40</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>23</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>19</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>21</v>
+      </c>
+      <c r="BH122" t="n">
         <v>13.9</v>
       </c>
-      <c r="BE122" t="n">
+      <c r="BI122" t="n">
         <v>13.9</v>
       </c>
-      <c r="BF122" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG122" t="n">
+      <c r="BJ122" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK122" t="n">
         <v>36.6</v>
       </c>
-      <c r="BH122" t="n">
-        <v>40</v>
-      </c>
-      <c r="BI122" t="n">
-        <v>23</v>
-      </c>
-      <c r="BJ122" t="n">
+      <c r="BL122" t="n">
         <v>182.1</v>
       </c>
     </row>
@@ -23593,24 +24329,30 @@
         <v>-103.6790983</v>
       </c>
       <c r="BD123" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="BE123" t="n">
+        <v>20</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>13</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>22</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI123" t="n">
         <v>126.7</v>
       </c>
-      <c r="BF123" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG123" t="n">
+      <c r="BJ123" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK123" t="n">
         <v>27.5</v>
       </c>
-      <c r="BH123" t="n">
-        <v>35</v>
-      </c>
-      <c r="BI123" t="n">
-        <v>20</v>
-      </c>
-      <c r="BJ123" t="n">
+      <c r="BL123" t="n">
         <v>104.5</v>
       </c>
     </row>
@@ -23779,24 +24521,30 @@
         <v>-104.4858267</v>
       </c>
       <c r="BD124" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="BE124" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="BF124" t="n">
+        <v>14</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>20</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ124" t="n">
         <v>101.6</v>
       </c>
-      <c r="BG124" t="n">
+      <c r="BK124" t="n">
         <v>101.6</v>
       </c>
-      <c r="BH124" t="n">
-        <v>34</v>
-      </c>
-      <c r="BI124" t="n">
-        <v>19</v>
-      </c>
-      <c r="BJ124" t="n">
+      <c r="BL124" t="n">
         <v>158.7</v>
       </c>
     </row>
@@ -23965,24 +24713,30 @@
         <v>-103.5123924</v>
       </c>
       <c r="BD125" t="n">
+        <v>24</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>19</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>8</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>16</v>
+      </c>
+      <c r="BH125" t="n">
         <v>28.9</v>
       </c>
-      <c r="BE125" t="n">
+      <c r="BI125" t="n">
         <v>48.2</v>
       </c>
-      <c r="BF125" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG125" t="n">
+      <c r="BJ125" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK125" t="n">
         <v>14.3</v>
       </c>
-      <c r="BH125" t="n">
-        <v>24</v>
-      </c>
-      <c r="BI125" t="n">
-        <v>19</v>
-      </c>
-      <c r="BJ125" t="n">
+      <c r="BL125" t="n">
         <v>112.2</v>
       </c>
     </row>
@@ -24151,24 +24905,30 @@
         <v>-102.868113</v>
       </c>
       <c r="BD126" t="n">
+        <v>14</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>10</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>8</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>6</v>
+      </c>
+      <c r="BH126" t="n">
         <v>45</v>
       </c>
-      <c r="BE126" t="n">
+      <c r="BI126" t="n">
         <v>45</v>
       </c>
-      <c r="BF126" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG126" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH126" t="n">
-        <v>14</v>
-      </c>
-      <c r="BI126" t="n">
-        <v>10</v>
-      </c>
       <c r="BJ126" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL126" t="n">
         <v>99.90000000000001</v>
       </c>
     </row>
